--- a/25-경기철도-수원시-보고서.xlsx
+++ b/25-경기철도-수원시-보고서.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\GSMM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\GSMM\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AFBC18-96A3-4F84-A888-E71CFD551469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB16854B-2942-4DA1-845A-360A2C815985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23040" yWindow="12" windowWidth="23256" windowHeight="12972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="152">
   <si>
     <t>시행년도</t>
   </si>
@@ -400,6 +400,142 @@
   </si>
   <si>
     <t>보통</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영통구 하동 147-144</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영통구 하동 968-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>법조타운 사거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영통구 이의동 1381-24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 1381-25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 1304-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>센트럴파크로 사거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영통구 하동 1015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영통구 하동 1016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영통구 하동 1016-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>컨벤션센터 사거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영통구 하동 1017-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 1337</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 1338</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도청사거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영통구 이의동 1342</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 1344</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영통구 이의동 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 262-7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 1332</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광교고사거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 1331</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 885-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 884</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 1329</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 1381-27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 1322-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 421-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 835</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광교사거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 1379-7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 432-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이의동 433</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>역사공원삼거리</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -605,6 +741,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -613,10 +753,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4720,7 +4856,9 @@
         <v>일반</v>
       </c>
       <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
+      <c r="Q6" s="4" t="s">
+        <v>118</v>
+      </c>
       <c r="R6" s="4"/>
       <c r="S6" s="5" t="s">
         <v>28</v>
@@ -4782,7 +4920,9 @@
         <v>일반</v>
       </c>
       <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
+      <c r="Q7" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="R7" s="4"/>
       <c r="S7" s="5" t="s">
         <v>30</v>
@@ -4844,7 +4984,9 @@
         <v>일반</v>
       </c>
       <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
+      <c r="Q8" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="R8" s="4"/>
       <c r="S8" s="5" t="s">
         <v>31</v>
@@ -4906,7 +5048,9 @@
         <v>일반</v>
       </c>
       <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
+      <c r="Q9" s="4" t="s">
+        <v>121</v>
+      </c>
       <c r="R9" s="4"/>
       <c r="S9" s="5" t="s">
         <v>32</v>
@@ -4968,7 +5112,9 @@
         <v>일반</v>
       </c>
       <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
+      <c r="Q10" s="4" t="s">
+        <v>122</v>
+      </c>
       <c r="R10" s="4"/>
       <c r="S10" s="5" t="s">
         <v>34</v>
@@ -5032,7 +5178,9 @@
       <c r="P11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="Q11" s="4"/>
+      <c r="Q11" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="R11" s="4"/>
       <c r="S11" s="5" t="s">
         <v>36</v>
@@ -5094,7 +5242,9 @@
         <v>일반</v>
       </c>
       <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
+      <c r="Q12" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="R12" s="4"/>
       <c r="S12" s="5" t="s">
         <v>37</v>
@@ -5156,7 +5306,9 @@
         <v>일반</v>
       </c>
       <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
+      <c r="Q13" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="R13" s="4"/>
       <c r="S13" s="5" t="s">
         <v>38</v>
@@ -5218,7 +5370,9 @@
         <v>일반</v>
       </c>
       <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
+      <c r="Q14" s="4" t="s">
+        <v>126</v>
+      </c>
       <c r="R14" s="4"/>
       <c r="S14" s="5" t="s">
         <v>39</v>
@@ -5282,7 +5436,9 @@
       <c r="P15" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="Q15" s="4"/>
+      <c r="Q15" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="R15" s="4"/>
       <c r="S15" s="5" t="s">
         <v>40</v>
@@ -5344,7 +5500,9 @@
         <v>일반</v>
       </c>
       <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
+      <c r="Q16" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="R16" s="4"/>
       <c r="S16" s="5" t="s">
         <v>41</v>
@@ -5406,7 +5564,9 @@
         <v>일반</v>
       </c>
       <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
+      <c r="Q17" s="4" t="s">
+        <v>129</v>
+      </c>
       <c r="R17" s="4"/>
       <c r="S17" s="5" t="s">
         <v>42</v>
@@ -5470,7 +5630,9 @@
       <c r="P18" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="Q18" s="4"/>
+      <c r="Q18" s="4" t="s">
+        <v>130</v>
+      </c>
       <c r="R18" s="4"/>
       <c r="S18" s="5" t="s">
         <v>43</v>
@@ -5532,7 +5694,9 @@
         <v>일반</v>
       </c>
       <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
+      <c r="Q19" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="R19" s="4"/>
       <c r="S19" s="5" t="s">
         <v>45</v>
@@ -5594,7 +5758,9 @@
         <v>일반</v>
       </c>
       <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
+      <c r="Q20" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="R20" s="4"/>
       <c r="S20" s="5" t="s">
         <v>47</v>
@@ -5656,7 +5822,9 @@
         <v>일반</v>
       </c>
       <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
+      <c r="Q21" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="R21" s="4"/>
       <c r="S21" s="5" t="s">
         <v>48</v>
@@ -5718,7 +5886,9 @@
         <v>일반</v>
       </c>
       <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
+      <c r="Q22" s="4" t="s">
+        <v>133</v>
+      </c>
       <c r="R22" s="4"/>
       <c r="S22" s="5" t="s">
         <v>49</v>
@@ -5780,7 +5950,9 @@
         <v>일반</v>
       </c>
       <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
+      <c r="Q23" s="4" t="s">
+        <v>136</v>
+      </c>
       <c r="R23" s="4"/>
       <c r="S23" s="5" t="s">
         <v>50</v>
@@ -5842,7 +6014,9 @@
         <v>일반</v>
       </c>
       <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
+      <c r="Q24" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="R24" s="4"/>
       <c r="S24" s="5" t="s">
         <v>51</v>
@@ -5906,7 +6080,9 @@
       <c r="P25" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="Q25" s="4"/>
+      <c r="Q25" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="R25" s="4"/>
       <c r="S25" s="5" t="s">
         <v>53</v>
@@ -5968,7 +6144,9 @@
         <v>일반</v>
       </c>
       <c r="P26" s="4"/>
-      <c r="Q26" s="4"/>
+      <c r="Q26" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="R26" s="4"/>
       <c r="S26" s="5" t="s">
         <v>54</v>
@@ -6030,7 +6208,9 @@
         <v>일반</v>
       </c>
       <c r="P27" s="4"/>
-      <c r="Q27" s="4"/>
+      <c r="Q27" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="R27" s="4"/>
       <c r="S27" s="5" t="s">
         <v>55</v>
@@ -6092,7 +6272,9 @@
         <v>일반</v>
       </c>
       <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
+      <c r="Q28" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="R28" s="4"/>
       <c r="S28" s="5" t="s">
         <v>56</v>
@@ -6154,7 +6336,9 @@
         <v>일반</v>
       </c>
       <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
+      <c r="Q29" s="4" t="s">
+        <v>139</v>
+      </c>
       <c r="R29" s="4"/>
       <c r="S29" s="5" t="s">
         <v>57</v>
@@ -6216,7 +6400,9 @@
         <v>일반</v>
       </c>
       <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
+      <c r="Q30" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="R30" s="4"/>
       <c r="S30" s="5" t="s">
         <v>59</v>
@@ -6280,7 +6466,9 @@
       <c r="P31" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="Q31" s="4"/>
+      <c r="Q31" s="4" t="s">
+        <v>141</v>
+      </c>
       <c r="R31" s="4"/>
       <c r="S31" s="5" t="s">
         <v>61</v>
@@ -6342,7 +6530,9 @@
         <v>일반</v>
       </c>
       <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
+      <c r="Q32" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="R32" s="4"/>
       <c r="S32" s="5" t="s">
         <v>62</v>
@@ -6404,7 +6594,9 @@
         <v>일반</v>
       </c>
       <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
+      <c r="Q33" s="4" t="s">
+        <v>142</v>
+      </c>
       <c r="R33" s="4"/>
       <c r="S33" s="5" t="s">
         <v>63</v>
@@ -6466,7 +6658,9 @@
         <v>일반</v>
       </c>
       <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
+      <c r="Q34" s="4" t="s">
+        <v>141</v>
+      </c>
       <c r="R34" s="4"/>
       <c r="S34" s="5" t="s">
         <v>64</v>
@@ -6528,7 +6722,9 @@
         <v>일반</v>
       </c>
       <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
+      <c r="Q35" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="R35" s="4"/>
       <c r="S35" s="5" t="s">
         <v>65</v>
@@ -6592,7 +6788,9 @@
       <c r="P36" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="Q36" s="4"/>
+      <c r="Q36" s="4" t="s">
+        <v>145</v>
+      </c>
       <c r="R36" s="4"/>
       <c r="S36" s="5" t="s">
         <v>67</v>
@@ -6654,7 +6852,9 @@
         <v>일반</v>
       </c>
       <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
+      <c r="Q37" s="4" t="s">
+        <v>145</v>
+      </c>
       <c r="R37" s="4"/>
       <c r="S37" s="5" t="s">
         <v>68</v>
@@ -6718,7 +6918,9 @@
       <c r="P38" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="Q38" s="4"/>
+      <c r="Q38" s="4" t="s">
+        <v>145</v>
+      </c>
       <c r="R38" s="4"/>
       <c r="S38" s="5" t="s">
         <v>70</v>
@@ -6780,7 +6982,9 @@
         <v>일반</v>
       </c>
       <c r="P39" s="4"/>
-      <c r="Q39" s="4"/>
+      <c r="Q39" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="R39" s="4"/>
       <c r="S39" s="5" t="s">
         <v>71</v>
@@ -6842,7 +7046,9 @@
         <v>일반</v>
       </c>
       <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
+      <c r="Q40" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="R40" s="4"/>
       <c r="S40" s="5" t="s">
         <v>73</v>
@@ -6906,7 +7112,9 @@
       <c r="P41" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="Q41" s="4"/>
+      <c r="Q41" s="4" t="s">
+        <v>148</v>
+      </c>
       <c r="R41" s="4"/>
       <c r="S41" s="5" t="s">
         <v>75</v>
@@ -6970,7 +7178,9 @@
       <c r="P42" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="Q42" s="4"/>
+      <c r="Q42" s="4" t="s">
+        <v>149</v>
+      </c>
       <c r="R42" s="4"/>
       <c r="S42" s="5" t="s">
         <v>77</v>
@@ -7034,7 +7244,9 @@
       <c r="P43" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="Q43" s="4"/>
+      <c r="Q43" s="4" t="s">
+        <v>150</v>
+      </c>
       <c r="R43" s="4"/>
       <c r="S43" s="5" t="s">
         <v>78</v>
@@ -7096,7 +7308,9 @@
         <v>일반</v>
       </c>
       <c r="P44" s="4"/>
-      <c r="Q44" s="4"/>
+      <c r="Q44" s="4" t="s">
+        <v>150</v>
+      </c>
       <c r="R44" s="4"/>
       <c r="S44" s="5" t="s">
         <v>79</v>
@@ -7160,7 +7374,9 @@
       <c r="P45" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="Q45" s="4"/>
+      <c r="Q45" s="4" t="s">
+        <v>151</v>
+      </c>
       <c r="R45" s="4"/>
       <c r="S45" s="5" t="s">
         <v>80</v>
@@ -7222,7 +7438,9 @@
         <v>일반</v>
       </c>
       <c r="P46" s="4"/>
-      <c r="Q46" s="4"/>
+      <c r="Q46" s="4" t="s">
+        <v>151</v>
+      </c>
       <c r="R46" s="4"/>
       <c r="S46" s="5" t="s">
         <v>80</v>
@@ -7819,64 +8037,64 @@
       <c r="P3" s="9"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="22" t="s">
+      <c r="B4" s="26"/>
+      <c r="C4" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="24"/>
-      <c r="E4" s="22" t="s">
+      <c r="D4" s="26"/>
+      <c r="E4" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="F4" s="24"/>
-      <c r="G4" s="22" t="s">
+      <c r="F4" s="26"/>
+      <c r="G4" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="H4" s="23"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="22" t="s">
+      <c r="H4" s="25"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="K4" s="23"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="22" t="s">
+      <c r="K4" s="25"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="24"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="26"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="22" t="s">
+      <c r="B5" s="26"/>
+      <c r="C5" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="22" t="s">
+      <c r="D5" s="26"/>
+      <c r="E5" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="24"/>
-      <c r="G5" s="22" t="s">
+      <c r="F5" s="26"/>
+      <c r="G5" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="22" t="s">
+      <c r="H5" s="25"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="K5" s="23"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="22" t="s">
+      <c r="K5" s="25"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="24"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="26"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
@@ -7897,43 +8115,43 @@
       <c r="P6" s="9"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="25" t="s">
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="26" t="s">
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="26" t="s">
+      <c r="O7" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="P7" s="26" t="s">
+      <c r="P7" s="22" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
       <c r="D8" s="19" t="s">
         <v>8</v>
       </c>
@@ -7964,9 +8182,9 @@
       <c r="M8" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="N8" s="27"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="27"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
       <c r="Q8"/>
       <c r="R8"/>
       <c r="S8"/>
@@ -10705,14 +10923,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="B7:B8"/>
     <mergeCell ref="M4:P4"/>
     <mergeCell ref="I7:M7"/>
     <mergeCell ref="G5:I5"/>
@@ -10725,6 +10935,14 @@
     <mergeCell ref="N7:N8"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="B7:B8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/25-경기철도-수원시-보고서.xlsx
+++ b/25-경기철도-수원시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T51"/>
+  <dimension ref="A1:T61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3272,7 +3272,7 @@
         <v xml:space="preserve">지하차도 내 </v>
       </c>
       <c r="T49" t="str">
-        <v>현장확인필요</v>
+        <v>내용확인필요</v>
       </c>
     </row>
     <row r="50">
@@ -3334,7 +3334,7 @@
         <v>지하차도 앞</v>
       </c>
       <c r="T50" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -3396,12 +3396,632 @@
         <v>광교더리브아파트6209동 앞 도로(센트럴파크로34)</v>
       </c>
       <c r="T51" t="str">
-        <v>현장확인필요</v>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>26-07</v>
+      </c>
+      <c r="B52" t="str">
+        <v>광교중앙로</v>
+      </c>
+      <c r="C52" t="str">
+        <v>26-수원시-07</v>
+      </c>
+      <c r="D52" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E52" t="str">
+        <v>양호</v>
+      </c>
+      <c r="F52" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G52" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H52" t="str">
+        <v>-</v>
+      </c>
+      <c r="I52" t="str">
+        <v>0</v>
+      </c>
+      <c r="J52" t="str">
+        <v>0</v>
+      </c>
+      <c r="K52" t="str">
+        <v>0</v>
+      </c>
+      <c r="L52" t="str">
+        <v>1</v>
+      </c>
+      <c r="M52" t="str">
+        <v>0</v>
+      </c>
+      <c r="N52" t="str">
+        <v>1</v>
+      </c>
+      <c r="O52" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P52" t="str">
+        <v>패칭3x20m</v>
+      </c>
+      <c r="Q52" t="str">
+        <v>이의동1304</v>
+      </c>
+      <c r="R52" t="str">
+        <v/>
+      </c>
+      <c r="S52" t="str">
+        <v>래미안광교아파트 6303동 환기구피난계단 앞 도로(센트럴파크로60)</v>
+      </c>
+      <c r="T52" t="str">
+        <v>내용확인필요</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>26-08</v>
+      </c>
+      <c r="B53" t="str">
+        <v>광교중앙로</v>
+      </c>
+      <c r="C53" t="str">
+        <v>26-수원시-08</v>
+      </c>
+      <c r="D53" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E53" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F53" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G53" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H53" t="str">
+        <v>-</v>
+      </c>
+      <c r="I53" t="str">
+        <v>0</v>
+      </c>
+      <c r="J53" t="str">
+        <v>3</v>
+      </c>
+      <c r="K53" t="str">
+        <v>0</v>
+      </c>
+      <c r="L53" t="str">
+        <v>1</v>
+      </c>
+      <c r="M53" t="str">
+        <v>0</v>
+      </c>
+      <c r="N53" t="str">
+        <v>4</v>
+      </c>
+      <c r="O53" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P53" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q53" t="str">
+        <v>이의동1334-1</v>
+      </c>
+      <c r="R53" t="str">
+        <v/>
+      </c>
+      <c r="S53" t="str">
+        <v>등포칼국수 건너편 도로</v>
+      </c>
+      <c r="T53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>26-09</v>
+      </c>
+      <c r="B54" t="str">
+        <v>광교중앙로</v>
+      </c>
+      <c r="C54" t="str">
+        <v>26-수원시-09</v>
+      </c>
+      <c r="D54" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E54" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F54" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G54" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H54" t="str">
+        <v>-</v>
+      </c>
+      <c r="I54" t="str">
+        <v>0</v>
+      </c>
+      <c r="J54" t="str">
+        <v>3</v>
+      </c>
+      <c r="K54" t="str">
+        <v>0</v>
+      </c>
+      <c r="L54" t="str">
+        <v>1</v>
+      </c>
+      <c r="M54" t="str">
+        <v>0</v>
+      </c>
+      <c r="N54" t="str">
+        <v>4</v>
+      </c>
+      <c r="O54" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P54" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q54" t="str">
+        <v>이의동1334</v>
+      </c>
+      <c r="R54" t="str">
+        <v/>
+      </c>
+      <c r="S54" t="str">
+        <v>광교센트럴뷰아파트6013동 버스정류장 앞 도로(센트럴타운로22번길36)</v>
+      </c>
+      <c r="T54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>26-10</v>
+      </c>
+      <c r="B55" t="str">
+        <v>광교중앙로</v>
+      </c>
+      <c r="C55" t="str">
+        <v>26-수원시-10</v>
+      </c>
+      <c r="D55" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E55" t="str">
+        <v>종횡균열</v>
+      </c>
+      <c r="F55" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G55" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H55" t="str">
+        <v>-</v>
+      </c>
+      <c r="I55" t="str">
+        <v>0</v>
+      </c>
+      <c r="J55" t="str">
+        <v>1</v>
+      </c>
+      <c r="K55" t="str">
+        <v>0</v>
+      </c>
+      <c r="L55" t="str">
+        <v>1</v>
+      </c>
+      <c r="M55" t="str">
+        <v>0</v>
+      </c>
+      <c r="N55" t="str">
+        <v>2</v>
+      </c>
+      <c r="O55" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P55" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q55" t="str">
+        <v>이의동1334-3</v>
+      </c>
+      <c r="R55" t="str">
+        <v/>
+      </c>
+      <c r="S55" t="str">
+        <v>컨베션센터 사거리</v>
+      </c>
+      <c r="T55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>26-11</v>
+      </c>
+      <c r="B56" t="str">
+        <v>광교중앙로</v>
+      </c>
+      <c r="C56" t="str">
+        <v>26-수원시-11</v>
+      </c>
+      <c r="D56" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E56" t="str">
+        <v>양호</v>
+      </c>
+      <c r="F56" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G56" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H56" t="str">
+        <v>-</v>
+      </c>
+      <c r="I56" t="str">
+        <v>0</v>
+      </c>
+      <c r="J56" t="str">
+        <v>0</v>
+      </c>
+      <c r="K56" t="str">
+        <v>0</v>
+      </c>
+      <c r="L56" t="str">
+        <v>1</v>
+      </c>
+      <c r="M56" t="str">
+        <v>0</v>
+      </c>
+      <c r="N56" t="str">
+        <v>1</v>
+      </c>
+      <c r="O56" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P56" t="str">
+        <v>패칭3x30m</v>
+      </c>
+      <c r="Q56" t="str">
+        <v>이의동1336-1</v>
+      </c>
+      <c r="R56" t="str">
+        <v/>
+      </c>
+      <c r="S56" t="str">
+        <v>광교엘포트 아이파크오피스텔 스타벅스 버스정류장 앞 도로(광교중앙로145)</v>
+      </c>
+      <c r="T56" t="str">
+        <v>내용확인필요</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>26-12</v>
+      </c>
+      <c r="B57" t="str">
+        <v>광교중앙로</v>
+      </c>
+      <c r="C57" t="str">
+        <v>26-수원시-12</v>
+      </c>
+      <c r="D57" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E57" t="str">
+        <v>양호</v>
+      </c>
+      <c r="F57" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G57" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H57" t="str">
+        <v>-</v>
+      </c>
+      <c r="I57" t="str">
+        <v>0</v>
+      </c>
+      <c r="J57" t="str">
+        <v>0</v>
+      </c>
+      <c r="K57" t="str">
+        <v>0</v>
+      </c>
+      <c r="L57" t="str">
+        <v>1</v>
+      </c>
+      <c r="M57" t="str">
+        <v>0</v>
+      </c>
+      <c r="N57" t="str">
+        <v>1</v>
+      </c>
+      <c r="O57" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P57" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q57" t="str">
+        <v>하동1017</v>
+      </c>
+      <c r="R57" t="str">
+        <v/>
+      </c>
+      <c r="S57" t="str">
+        <v>수원컨벤션센터 버스정류장 앞 도로(광교중앙로140)</v>
+      </c>
+      <c r="T57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>26-13</v>
+      </c>
+      <c r="B58" t="str">
+        <v>도청로</v>
+      </c>
+      <c r="C58" t="str">
+        <v>26-수원시-13</v>
+      </c>
+      <c r="D58" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E58" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F58" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G58" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H58" t="str">
+        <v>-</v>
+      </c>
+      <c r="I58" t="str">
+        <v>0</v>
+      </c>
+      <c r="J58" t="str">
+        <v>3</v>
+      </c>
+      <c r="K58" t="str">
+        <v>0</v>
+      </c>
+      <c r="L58" t="str">
+        <v>1</v>
+      </c>
+      <c r="M58" t="str">
+        <v>0</v>
+      </c>
+      <c r="N58" t="str">
+        <v>4</v>
+      </c>
+      <c r="O58" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P58" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q58" t="str">
+        <v>이의동1338</v>
+      </c>
+      <c r="R58" t="str">
+        <v/>
+      </c>
+      <c r="S58" t="str">
+        <v>롯데몰 주차장 출입로 앞 도로(도청로10)</v>
+      </c>
+      <c r="T58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>26-14</v>
+      </c>
+      <c r="B59" t="str">
+        <v>도청로</v>
+      </c>
+      <c r="C59" t="str">
+        <v>26-수원시-14</v>
+      </c>
+      <c r="D59" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E59" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F59" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G59" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H59" t="str">
+        <v>-</v>
+      </c>
+      <c r="I59" t="str">
+        <v>0</v>
+      </c>
+      <c r="J59" t="str">
+        <v>3</v>
+      </c>
+      <c r="K59" t="str">
+        <v>0</v>
+      </c>
+      <c r="L59" t="str">
+        <v>1</v>
+      </c>
+      <c r="M59" t="str">
+        <v>0</v>
+      </c>
+      <c r="N59" t="str">
+        <v>4</v>
+      </c>
+      <c r="O59" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P59" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q59" t="str">
+        <v>이의동198</v>
+      </c>
+      <c r="R59" t="str">
+        <v/>
+      </c>
+      <c r="S59" t="str">
+        <v>도청사거리</v>
+      </c>
+      <c r="T59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>26-15</v>
+      </c>
+      <c r="B60" t="str">
+        <v>도청로</v>
+      </c>
+      <c r="C60" t="str">
+        <v>26-수원시-15</v>
+      </c>
+      <c r="D60" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E60" t="str">
+        <v>횡균열</v>
+      </c>
+      <c r="F60" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G60" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H60" t="str">
+        <v>-</v>
+      </c>
+      <c r="I60" t="str">
+        <v>0</v>
+      </c>
+      <c r="J60" t="str">
+        <v>1</v>
+      </c>
+      <c r="K60" t="str">
+        <v>0</v>
+      </c>
+      <c r="L60" t="str">
+        <v>1</v>
+      </c>
+      <c r="M60" t="str">
+        <v>0</v>
+      </c>
+      <c r="N60" t="str">
+        <v>2</v>
+      </c>
+      <c r="O60" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P60" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q60" t="str">
+        <v>이의동262</v>
+      </c>
+      <c r="R60" t="str">
+        <v/>
+      </c>
+      <c r="S60" t="str">
+        <v>경기도서관 주차장 입구 앞(도청로40)</v>
+      </c>
+      <c r="T60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>26-16</v>
+      </c>
+      <c r="B61" t="str">
+        <v>도청로</v>
+      </c>
+      <c r="C61" t="str">
+        <v>26-수원시-16</v>
+      </c>
+      <c r="D61" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E61" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F61" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G61" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H61" t="str">
+        <v>-</v>
+      </c>
+      <c r="I61" t="str">
+        <v>0</v>
+      </c>
+      <c r="J61" t="str">
+        <v>3</v>
+      </c>
+      <c r="K61" t="str">
+        <v>0</v>
+      </c>
+      <c r="L61" t="str">
+        <v>1</v>
+      </c>
+      <c r="M61" t="str">
+        <v>0</v>
+      </c>
+      <c r="N61" t="str">
+        <v>4</v>
+      </c>
+      <c r="O61" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P61" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q61" t="str">
+        <v>이의동262-7</v>
+      </c>
+      <c r="R61" t="str">
+        <v/>
+      </c>
+      <c r="S61" t="str">
+        <v>경기도서관 정문 앞 도로(도청로40)</v>
+      </c>
+      <c r="T61" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T61"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-수원시-보고서.xlsx
+++ b/25-경기철도-수원시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T61"/>
+  <dimension ref="A1:T68"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4019,9 +4019,443 @@
         <v/>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>26-17</v>
+      </c>
+      <c r="B62" t="str">
+        <v>도청로</v>
+      </c>
+      <c r="C62" t="str">
+        <v>26-수원시-17</v>
+      </c>
+      <c r="D62" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E62" t="str">
+        <v>종균열</v>
+      </c>
+      <c r="F62" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G62" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H62" t="str">
+        <v>-</v>
+      </c>
+      <c r="I62" t="str">
+        <v>0</v>
+      </c>
+      <c r="J62" t="str">
+        <v>1</v>
+      </c>
+      <c r="K62" t="str">
+        <v>0</v>
+      </c>
+      <c r="L62" t="str">
+        <v>1</v>
+      </c>
+      <c r="M62" t="str">
+        <v>0</v>
+      </c>
+      <c r="N62" t="str">
+        <v>2</v>
+      </c>
+      <c r="O62" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P62" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q62" t="str">
+        <v>이의동1332</v>
+      </c>
+      <c r="R62" t="str">
+        <v/>
+      </c>
+      <c r="S62" t="str">
+        <v>아브뉴프랑_광교점 아티제 앞 횡단보도(센트럴타운로85)</v>
+      </c>
+      <c r="T62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>26-18</v>
+      </c>
+      <c r="B63" t="str">
+        <v>도청로</v>
+      </c>
+      <c r="C63" t="str">
+        <v>26-수원시-18</v>
+      </c>
+      <c r="D63" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E63" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F63" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G63" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H63" t="str">
+        <v>-</v>
+      </c>
+      <c r="I63" t="str">
+        <v>0</v>
+      </c>
+      <c r="J63" t="str">
+        <v>3</v>
+      </c>
+      <c r="K63" t="str">
+        <v>0</v>
+      </c>
+      <c r="L63" t="str">
+        <v>1</v>
+      </c>
+      <c r="M63" t="str">
+        <v>0</v>
+      </c>
+      <c r="N63" t="str">
+        <v>4</v>
+      </c>
+      <c r="O63" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P63" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q63" t="str">
+        <v>이의동1344</v>
+      </c>
+      <c r="R63" t="str">
+        <v/>
+      </c>
+      <c r="S63" t="str">
+        <v>소중한집 인테리어_광교점 앞 도로(도청로65 상가1동)</v>
+      </c>
+      <c r="T63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>26-19</v>
+      </c>
+      <c r="B64" t="str">
+        <v>도청로</v>
+      </c>
+      <c r="C64" t="str">
+        <v>26-수원시-19</v>
+      </c>
+      <c r="D64" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E64" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F64" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G64" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H64" t="str">
+        <v>-</v>
+      </c>
+      <c r="I64" t="str">
+        <v>0</v>
+      </c>
+      <c r="J64" t="str">
+        <v>3</v>
+      </c>
+      <c r="K64" t="str">
+        <v>0</v>
+      </c>
+      <c r="L64" t="str">
+        <v>1</v>
+      </c>
+      <c r="M64" t="str">
+        <v>0</v>
+      </c>
+      <c r="N64" t="str">
+        <v>4</v>
+      </c>
+      <c r="O64" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P64" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q64" t="str">
+        <v>이의동1381-11</v>
+      </c>
+      <c r="R64" t="str">
+        <v/>
+      </c>
+      <c r="S64" t="str">
+        <v>광교고사거리</v>
+      </c>
+      <c r="T64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>26-20</v>
+      </c>
+      <c r="B65" t="str">
+        <v>광교로</v>
+      </c>
+      <c r="C65" t="str">
+        <v>26-수원시-20</v>
+      </c>
+      <c r="D65" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E65" t="str">
+        <v>횡균열</v>
+      </c>
+      <c r="F65" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G65" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H65" t="str">
+        <v>-</v>
+      </c>
+      <c r="I65" t="str">
+        <v>0</v>
+      </c>
+      <c r="J65" t="str">
+        <v>1</v>
+      </c>
+      <c r="K65" t="str">
+        <v>0</v>
+      </c>
+      <c r="L65" t="str">
+        <v>1</v>
+      </c>
+      <c r="M65" t="str">
+        <v>0</v>
+      </c>
+      <c r="N65" t="str">
+        <v>2</v>
+      </c>
+      <c r="O65" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P65" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q65" t="str">
+        <v>이의동885-1</v>
+      </c>
+      <c r="R65" t="str">
+        <v/>
+      </c>
+      <c r="S65" t="str">
+        <v>차세대 융합기술연구원 앞 횡단보도</v>
+      </c>
+      <c r="T65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>26-21</v>
+      </c>
+      <c r="B66" t="str">
+        <v>광교로</v>
+      </c>
+      <c r="C66" t="str">
+        <v>26-수원시-21</v>
+      </c>
+      <c r="D66" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E66" t="str">
+        <v>종균열</v>
+      </c>
+      <c r="F66" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G66" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H66" t="str">
+        <v>-</v>
+      </c>
+      <c r="I66" t="str">
+        <v>0</v>
+      </c>
+      <c r="J66" t="str">
+        <v>1</v>
+      </c>
+      <c r="K66" t="str">
+        <v>0</v>
+      </c>
+      <c r="L66" t="str">
+        <v>1</v>
+      </c>
+      <c r="M66" t="str">
+        <v>0</v>
+      </c>
+      <c r="N66" t="str">
+        <v>2</v>
+      </c>
+      <c r="O66" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P66" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q66" t="str">
+        <v>이의동1329</v>
+      </c>
+      <c r="R66" t="str">
+        <v/>
+      </c>
+      <c r="S66" t="str">
+        <v>안효빌딩 현대자동차 앞 도로(광교로146)</v>
+      </c>
+      <c r="T66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>26-22</v>
+      </c>
+      <c r="B67" t="str">
+        <v>광교로</v>
+      </c>
+      <c r="C67" t="str">
+        <v>26-수원시-22</v>
+      </c>
+      <c r="D67" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E67" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F67" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G67" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H67" t="str">
+        <v>-</v>
+      </c>
+      <c r="I67" t="str">
+        <v>0</v>
+      </c>
+      <c r="J67" t="str">
+        <v>3</v>
+      </c>
+      <c r="K67" t="str">
+        <v>0</v>
+      </c>
+      <c r="L67" t="str">
+        <v>1</v>
+      </c>
+      <c r="M67" t="str">
+        <v>0</v>
+      </c>
+      <c r="N67" t="str">
+        <v>4</v>
+      </c>
+      <c r="O67" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P67" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q67" t="str">
+        <v>이의동884</v>
+      </c>
+      <c r="R67" t="str">
+        <v/>
+      </c>
+      <c r="S67" t="str">
+        <v>차세대 융합기술연구원 버스정류장 앞 도로</v>
+      </c>
+      <c r="T67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>26-23</v>
+      </c>
+      <c r="B68" t="str">
+        <v>광교로</v>
+      </c>
+      <c r="C68" t="str">
+        <v>26-수원시-23</v>
+      </c>
+      <c r="D68" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E68" t="str">
+        <v>종균열</v>
+      </c>
+      <c r="F68" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G68" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H68" t="str">
+        <v>-</v>
+      </c>
+      <c r="I68" t="str">
+        <v>0</v>
+      </c>
+      <c r="J68" t="str">
+        <v>1</v>
+      </c>
+      <c r="K68" t="str">
+        <v>0</v>
+      </c>
+      <c r="L68" t="str">
+        <v>1</v>
+      </c>
+      <c r="M68" t="str">
+        <v>0</v>
+      </c>
+      <c r="N68" t="str">
+        <v>2</v>
+      </c>
+      <c r="O68" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P68" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q68" t="str">
+        <v>이의동1322</v>
+      </c>
+      <c r="R68" t="str">
+        <v/>
+      </c>
+      <c r="S68" t="str">
+        <v>광교 비지니스센터 앞 도로(광교로152)</v>
+      </c>
+      <c r="T68" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T68"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-수원시-보고서.xlsx
+++ b/25-경기철도-수원시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T68"/>
+  <dimension ref="A1:T69"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4447,15 +4447,77 @@
         <v/>
       </c>
       <c r="S68" t="str">
-        <v>광교 비지니스센터 앞 도로(광교로152)</v>
+        <v>광교 비지니스센터 앞 도로(광교로152))</v>
       </c>
       <c r="T68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>26-24</v>
+      </c>
+      <c r="B69" t="str">
+        <v>광교로</v>
+      </c>
+      <c r="C69" t="str">
+        <v>26-수원시-24</v>
+      </c>
+      <c r="D69" t="str">
+        <v>불량</v>
+      </c>
+      <c r="E69" t="str">
+        <v>양호</v>
+      </c>
+      <c r="F69" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G69" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H69" t="str">
+        <v>22년07월_최초발생</v>
+      </c>
+      <c r="I69" t="str">
+        <v>9</v>
+      </c>
+      <c r="J69" t="str">
+        <v>0</v>
+      </c>
+      <c r="K69" t="str">
+        <v>0</v>
+      </c>
+      <c r="L69" t="str">
+        <v>1</v>
+      </c>
+      <c r="M69" t="str">
+        <v>0</v>
+      </c>
+      <c r="N69" t="str">
+        <v>10</v>
+      </c>
+      <c r="O69" t="str">
+        <v>긴급</v>
+      </c>
+      <c r="P69" t="str">
+        <v>10cm이상 보도침하</v>
+      </c>
+      <c r="Q69" t="str">
+        <v>이의동421-5</v>
+      </c>
+      <c r="R69" t="str">
+        <v/>
+      </c>
+      <c r="S69" t="str">
+        <v>입출고선환기구 옆 보도</v>
+      </c>
+      <c r="T69" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T68"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T69"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-수원시-보고서.xlsx
+++ b/25-경기철도-수원시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T69"/>
+  <dimension ref="A1:T71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4515,9 +4515,133 @@
         <v/>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>26-25</v>
+      </c>
+      <c r="B70" t="str">
+        <v>광교로</v>
+      </c>
+      <c r="C70" t="str">
+        <v>26-수원시-25</v>
+      </c>
+      <c r="D70" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E70" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F70" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G70" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H70" t="str">
+        <v>-</v>
+      </c>
+      <c r="I70" t="str">
+        <v>0</v>
+      </c>
+      <c r="J70" t="str">
+        <v>3</v>
+      </c>
+      <c r="K70" t="str">
+        <v>0</v>
+      </c>
+      <c r="L70" t="str">
+        <v>1</v>
+      </c>
+      <c r="M70" t="str">
+        <v>0</v>
+      </c>
+      <c r="N70" t="str">
+        <v>4</v>
+      </c>
+      <c r="O70" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P70" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q70" t="str">
+        <v>이의동421-5</v>
+      </c>
+      <c r="R70" t="str">
+        <v/>
+      </c>
+      <c r="S70" t="str">
+        <v>입출고선환기구 옆 도로</v>
+      </c>
+      <c r="T70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>26-26</v>
+      </c>
+      <c r="B71" t="str">
+        <v>광교로</v>
+      </c>
+      <c r="C71" t="str">
+        <v>26-수원시-26</v>
+      </c>
+      <c r="D71" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E71" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F71" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G71" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H71" t="str">
+        <v>-</v>
+      </c>
+      <c r="I71" t="str">
+        <v>0</v>
+      </c>
+      <c r="J71" t="str">
+        <v>3</v>
+      </c>
+      <c r="K71" t="str">
+        <v>0</v>
+      </c>
+      <c r="L71" t="str">
+        <v>1</v>
+      </c>
+      <c r="M71" t="str">
+        <v>0</v>
+      </c>
+      <c r="N71" t="str">
+        <v>4</v>
+      </c>
+      <c r="O71" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P71" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q71" t="str">
+        <v>이의동1322-2</v>
+      </c>
+      <c r="R71" t="str">
+        <v/>
+      </c>
+      <c r="S71" t="str">
+        <v>광교사거리 전 도로</v>
+      </c>
+      <c r="T71" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T71"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-수원시-보고서.xlsx
+++ b/25-경기철도-수원시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T71"/>
+  <dimension ref="A1:T68"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3227,7 +3227,7 @@
         <v>양호</v>
       </c>
       <c r="E49" t="str">
-        <v>양호</v>
+        <v>종균열</v>
       </c>
       <c r="F49" t="str">
         <v>양호</v>
@@ -3242,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="str">
         <v>0</v>
@@ -3254,13 +3254,13 @@
         <v>0</v>
       </c>
       <c r="N49" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O49" t="str">
         <v>일반</v>
       </c>
       <c r="P49" t="str">
-        <v>패칭3x10m</v>
+        <v>-</v>
       </c>
       <c r="Q49" t="str">
         <v>이의동1302-1</v>
@@ -3269,10 +3269,10 @@
         <v/>
       </c>
       <c r="S49" t="str">
-        <v xml:space="preserve">지하차도 내 </v>
+        <v>지하차도 앞</v>
       </c>
       <c r="T49" t="str">
-        <v>내용확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -3289,7 +3289,7 @@
         <v>양호</v>
       </c>
       <c r="E50" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F50" t="str">
         <v>양호</v>
@@ -3304,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K50" t="str">
         <v>0</v>
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="N50" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O50" t="str">
         <v>일반</v>
@@ -3325,13 +3325,13 @@
         <v>-</v>
       </c>
       <c r="Q50" t="str">
-        <v>이의동1302-1</v>
+        <v>하동1013</v>
       </c>
       <c r="R50" t="str">
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>지하차도 앞</v>
+        <v>광교더리브아파트6209동 앞 도로(센트럴파크로34)</v>
       </c>
       <c r="T50" t="str">
         <v/>
@@ -3387,13 +3387,13 @@
         <v>-</v>
       </c>
       <c r="Q51" t="str">
-        <v>하동1013</v>
+        <v>이의동1334-1</v>
       </c>
       <c r="R51" t="str">
         <v/>
       </c>
       <c r="S51" t="str">
-        <v>광교더리브아파트6209동 앞 도로(센트럴파크로34)</v>
+        <v>등포칼국수 건너편 도로</v>
       </c>
       <c r="T51" t="str">
         <v/>
@@ -3413,7 +3413,7 @@
         <v>양호</v>
       </c>
       <c r="E52" t="str">
-        <v>양호</v>
+        <v>거북등</v>
       </c>
       <c r="F52" t="str">
         <v>양호</v>
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K52" t="str">
         <v>0</v>
@@ -3440,25 +3440,25 @@
         <v>0</v>
       </c>
       <c r="N52" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O52" t="str">
         <v>일반</v>
       </c>
       <c r="P52" t="str">
-        <v>패칭3x20m</v>
+        <v>-</v>
       </c>
       <c r="Q52" t="str">
-        <v>이의동1304</v>
+        <v>이의동1334</v>
       </c>
       <c r="R52" t="str">
         <v/>
       </c>
       <c r="S52" t="str">
-        <v>래미안광교아파트 6303동 환기구피난계단 앞 도로(센트럴파크로60)</v>
+        <v>광교센트럴뷰아파트6013동 버스정류장 앞 도로(센트럴타운로22번길36)</v>
       </c>
       <c r="T52" t="str">
-        <v>내용확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -3475,7 +3475,7 @@
         <v>양호</v>
       </c>
       <c r="E53" t="str">
-        <v>거북등</v>
+        <v>종횡균열</v>
       </c>
       <c r="F53" t="str">
         <v>양호</v>
@@ -3490,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K53" t="str">
         <v>0</v>
@@ -3502,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="N53" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O53" t="str">
         <v>일반</v>
@@ -3511,13 +3511,13 @@
         <v>-</v>
       </c>
       <c r="Q53" t="str">
-        <v>이의동1334-1</v>
+        <v>이의동1334-3</v>
       </c>
       <c r="R53" t="str">
         <v/>
       </c>
       <c r="S53" t="str">
-        <v>등포칼국수 건너편 도로</v>
+        <v>컨베션센터 사거리</v>
       </c>
       <c r="T53" t="str">
         <v/>
@@ -3537,7 +3537,7 @@
         <v>양호</v>
       </c>
       <c r="E54" t="str">
-        <v>거북등</v>
+        <v>양호</v>
       </c>
       <c r="F54" t="str">
         <v>양호</v>
@@ -3552,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K54" t="str">
         <v>0</v>
@@ -3564,22 +3564,22 @@
         <v>0</v>
       </c>
       <c r="N54" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O54" t="str">
         <v>일반</v>
       </c>
       <c r="P54" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q54" t="str">
-        <v>이의동1334</v>
+        <v>하동1017</v>
       </c>
       <c r="R54" t="str">
         <v/>
       </c>
       <c r="S54" t="str">
-        <v>광교센트럴뷰아파트6013동 버스정류장 앞 도로(센트럴타운로22번길36)</v>
+        <v>수원컨벤션센터 버스정류장 앞 도로(광교중앙로140)</v>
       </c>
       <c r="T54" t="str">
         <v/>
@@ -3590,7 +3590,7 @@
         <v>26-10</v>
       </c>
       <c r="B55" t="str">
-        <v>광교중앙로</v>
+        <v>도청로</v>
       </c>
       <c r="C55" t="str">
         <v>26-수원시-10</v>
@@ -3599,7 +3599,7 @@
         <v>양호</v>
       </c>
       <c r="E55" t="str">
-        <v>종횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F55" t="str">
         <v>양호</v>
@@ -3614,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="J55" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K55" t="str">
         <v>0</v>
@@ -3626,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="N55" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O55" t="str">
         <v>일반</v>
@@ -3635,13 +3635,13 @@
         <v>-</v>
       </c>
       <c r="Q55" t="str">
-        <v>이의동1334-3</v>
+        <v>이의동1338</v>
       </c>
       <c r="R55" t="str">
         <v/>
       </c>
       <c r="S55" t="str">
-        <v>컨베션센터 사거리</v>
+        <v>롯데몰 주차장 출입로 앞 도로(도청로10)</v>
       </c>
       <c r="T55" t="str">
         <v/>
@@ -3652,7 +3652,7 @@
         <v>26-11</v>
       </c>
       <c r="B56" t="str">
-        <v>광교중앙로</v>
+        <v>도청로</v>
       </c>
       <c r="C56" t="str">
         <v>26-수원시-11</v>
@@ -3661,7 +3661,7 @@
         <v>양호</v>
       </c>
       <c r="E56" t="str">
-        <v>양호</v>
+        <v>거북등</v>
       </c>
       <c r="F56" t="str">
         <v>양호</v>
@@ -3676,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K56" t="str">
         <v>0</v>
@@ -3688,25 +3688,25 @@
         <v>0</v>
       </c>
       <c r="N56" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O56" t="str">
         <v>일반</v>
       </c>
       <c r="P56" t="str">
-        <v>패칭3x30m</v>
+        <v>-</v>
       </c>
       <c r="Q56" t="str">
-        <v>이의동1336-1</v>
+        <v>이의동198</v>
       </c>
       <c r="R56" t="str">
         <v/>
       </c>
       <c r="S56" t="str">
-        <v>광교엘포트 아이파크오피스텔 스타벅스 버스정류장 앞 도로(광교중앙로145)</v>
+        <v>도청사거리</v>
       </c>
       <c r="T56" t="str">
-        <v>내용확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -3714,7 +3714,7 @@
         <v>26-12</v>
       </c>
       <c r="B57" t="str">
-        <v>광교중앙로</v>
+        <v>도청로</v>
       </c>
       <c r="C57" t="str">
         <v>26-수원시-12</v>
@@ -3723,7 +3723,7 @@
         <v>양호</v>
       </c>
       <c r="E57" t="str">
-        <v>양호</v>
+        <v>횡균열</v>
       </c>
       <c r="F57" t="str">
         <v>양호</v>
@@ -3738,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="J57" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="str">
         <v>0</v>
@@ -3750,22 +3750,22 @@
         <v>0</v>
       </c>
       <c r="N57" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O57" t="str">
         <v>일반</v>
       </c>
       <c r="P57" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q57" t="str">
-        <v>하동1017</v>
+        <v>이의동262</v>
       </c>
       <c r="R57" t="str">
         <v/>
       </c>
       <c r="S57" t="str">
-        <v>수원컨벤션센터 버스정류장 앞 도로(광교중앙로140)</v>
+        <v>경기도서관 주차장 입구 앞(도청로40)</v>
       </c>
       <c r="T57" t="str">
         <v/>
@@ -3821,13 +3821,13 @@
         <v>-</v>
       </c>
       <c r="Q58" t="str">
-        <v>이의동1338</v>
+        <v>이의동262-7</v>
       </c>
       <c r="R58" t="str">
         <v/>
       </c>
       <c r="S58" t="str">
-        <v>롯데몰 주차장 출입로 앞 도로(도청로10)</v>
+        <v>경기도서관 정문 앞 도로(도청로40)</v>
       </c>
       <c r="T58" t="str">
         <v/>
@@ -3847,7 +3847,7 @@
         <v>양호</v>
       </c>
       <c r="E59" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F59" t="str">
         <v>양호</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="J59" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K59" t="str">
         <v>0</v>
@@ -3874,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="N59" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O59" t="str">
         <v>일반</v>
@@ -3883,13 +3883,13 @@
         <v>-</v>
       </c>
       <c r="Q59" t="str">
-        <v>이의동198</v>
+        <v>이의동1332</v>
       </c>
       <c r="R59" t="str">
         <v/>
       </c>
       <c r="S59" t="str">
-        <v>도청사거리</v>
+        <v>아브뉴프랑_광교점 아티제 앞 횡단보도(센트럴타운로85)</v>
       </c>
       <c r="T59" t="str">
         <v/>
@@ -3909,7 +3909,7 @@
         <v>양호</v>
       </c>
       <c r="E60" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F60" t="str">
         <v>양호</v>
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="J60" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K60" t="str">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="N60" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O60" t="str">
         <v>일반</v>
@@ -3945,13 +3945,13 @@
         <v>-</v>
       </c>
       <c r="Q60" t="str">
-        <v>이의동262</v>
+        <v>이의동1344</v>
       </c>
       <c r="R60" t="str">
         <v/>
       </c>
       <c r="S60" t="str">
-        <v>경기도서관 주차장 입구 앞(도청로40)</v>
+        <v>소중한집 인테리어_광교점 앞 도로(도청로65 상가1동)</v>
       </c>
       <c r="T60" t="str">
         <v/>
@@ -4007,13 +4007,13 @@
         <v>-</v>
       </c>
       <c r="Q61" t="str">
-        <v>이의동262-7</v>
+        <v>이의동1381-11</v>
       </c>
       <c r="R61" t="str">
         <v/>
       </c>
       <c r="S61" t="str">
-        <v>경기도서관 정문 앞 도로(도청로40)</v>
+        <v>광교고사거리</v>
       </c>
       <c r="T61" t="str">
         <v/>
@@ -4024,7 +4024,7 @@
         <v>26-17</v>
       </c>
       <c r="B62" t="str">
-        <v>도청로</v>
+        <v>광교로</v>
       </c>
       <c r="C62" t="str">
         <v>26-수원시-17</v>
@@ -4033,7 +4033,7 @@
         <v>양호</v>
       </c>
       <c r="E62" t="str">
-        <v>종균열</v>
+        <v>횡균열</v>
       </c>
       <c r="F62" t="str">
         <v>양호</v>
@@ -4069,13 +4069,13 @@
         <v>-</v>
       </c>
       <c r="Q62" t="str">
-        <v>이의동1332</v>
+        <v>이의동885-1</v>
       </c>
       <c r="R62" t="str">
         <v/>
       </c>
       <c r="S62" t="str">
-        <v>아브뉴프랑_광교점 아티제 앞 횡단보도(센트럴타운로85)</v>
+        <v>차세대 융합기술연구원 앞 횡단보도</v>
       </c>
       <c r="T62" t="str">
         <v/>
@@ -4086,7 +4086,7 @@
         <v>26-18</v>
       </c>
       <c r="B63" t="str">
-        <v>도청로</v>
+        <v>광교로</v>
       </c>
       <c r="C63" t="str">
         <v>26-수원시-18</v>
@@ -4095,7 +4095,7 @@
         <v>양호</v>
       </c>
       <c r="E63" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F63" t="str">
         <v>양호</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K63" t="str">
         <v>0</v>
@@ -4122,7 +4122,7 @@
         <v>0</v>
       </c>
       <c r="N63" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O63" t="str">
         <v>일반</v>
@@ -4131,13 +4131,13 @@
         <v>-</v>
       </c>
       <c r="Q63" t="str">
-        <v>이의동1344</v>
+        <v>이의동1329</v>
       </c>
       <c r="R63" t="str">
         <v/>
       </c>
       <c r="S63" t="str">
-        <v>소중한집 인테리어_광교점 앞 도로(도청로65 상가1동)</v>
+        <v>안효빌딩 현대자동차 앞 도로(광교로146)</v>
       </c>
       <c r="T63" t="str">
         <v/>
@@ -4148,7 +4148,7 @@
         <v>26-19</v>
       </c>
       <c r="B64" t="str">
-        <v>도청로</v>
+        <v>광교로</v>
       </c>
       <c r="C64" t="str">
         <v>26-수원시-19</v>
@@ -4193,13 +4193,13 @@
         <v>-</v>
       </c>
       <c r="Q64" t="str">
-        <v>이의동1381-11</v>
+        <v>이의동884</v>
       </c>
       <c r="R64" t="str">
         <v/>
       </c>
       <c r="S64" t="str">
-        <v>광교고사거리</v>
+        <v>차세대 융합기술연구원 버스정류장 앞 도로</v>
       </c>
       <c r="T64" t="str">
         <v/>
@@ -4219,7 +4219,7 @@
         <v>양호</v>
       </c>
       <c r="E65" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F65" t="str">
         <v>양호</v>
@@ -4255,13 +4255,13 @@
         <v>-</v>
       </c>
       <c r="Q65" t="str">
-        <v>이의동885-1</v>
+        <v>이의동1322</v>
       </c>
       <c r="R65" t="str">
         <v/>
       </c>
       <c r="S65" t="str">
-        <v>차세대 융합기술연구원 앞 횡단보도</v>
+        <v>광교 비지니스센터 앞 도로(광교로152))</v>
       </c>
       <c r="T65" t="str">
         <v/>
@@ -4278,10 +4278,10 @@
         <v>26-수원시-21</v>
       </c>
       <c r="D66" t="str">
-        <v>양호</v>
+        <v>불량</v>
       </c>
       <c r="E66" t="str">
-        <v>종균열</v>
+        <v>양호</v>
       </c>
       <c r="F66" t="str">
         <v>양호</v>
@@ -4290,13 +4290,13 @@
         <v>10.3</v>
       </c>
       <c r="H66" t="str">
-        <v>-</v>
+        <v>22년07월_최초발생</v>
       </c>
       <c r="I66" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J66" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="str">
         <v>0</v>
@@ -4308,22 +4308,22 @@
         <v>0</v>
       </c>
       <c r="N66" t="str">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O66" t="str">
-        <v>일반</v>
+        <v>긴급</v>
       </c>
       <c r="P66" t="str">
-        <v>-</v>
+        <v>10cm이상 보도침하</v>
       </c>
       <c r="Q66" t="str">
-        <v>이의동1329</v>
+        <v>이의동421-5</v>
       </c>
       <c r="R66" t="str">
         <v/>
       </c>
       <c r="S66" t="str">
-        <v>안효빌딩 현대자동차 앞 도로(광교로146)</v>
+        <v>입출고선환기구 옆 보도</v>
       </c>
       <c r="T66" t="str">
         <v/>
@@ -4379,13 +4379,13 @@
         <v>-</v>
       </c>
       <c r="Q67" t="str">
-        <v>이의동884</v>
+        <v>이의동421-5</v>
       </c>
       <c r="R67" t="str">
         <v/>
       </c>
       <c r="S67" t="str">
-        <v>차세대 융합기술연구원 버스정류장 앞 도로</v>
+        <v>입출고선환기구 옆 도로</v>
       </c>
       <c r="T67" t="str">
         <v/>
@@ -4393,19 +4393,19 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>26-23</v>
+        <v>26-26</v>
       </c>
       <c r="B68" t="str">
         <v>광교로</v>
       </c>
       <c r="C68" t="str">
-        <v>26-수원시-23</v>
+        <v>26-수원시-26</v>
       </c>
       <c r="D68" t="str">
         <v>양호</v>
       </c>
       <c r="E68" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F68" t="str">
         <v>양호</v>
@@ -4420,7 +4420,7 @@
         <v>0</v>
       </c>
       <c r="J68" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K68" t="str">
         <v>0</v>
@@ -4432,7 +4432,7 @@
         <v>0</v>
       </c>
       <c r="N68" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O68" t="str">
         <v>일반</v>
@@ -4441,207 +4441,21 @@
         <v>-</v>
       </c>
       <c r="Q68" t="str">
-        <v>이의동1322</v>
+        <v>이의동1322-2</v>
       </c>
       <c r="R68" t="str">
         <v/>
       </c>
       <c r="S68" t="str">
-        <v>광교 비지니스센터 앞 도로(광교로152))</v>
+        <v>광교사거리 전 도로</v>
       </c>
       <c r="T68" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>26-24</v>
-      </c>
-      <c r="B69" t="str">
-        <v>광교로</v>
-      </c>
-      <c r="C69" t="str">
-        <v>26-수원시-24</v>
-      </c>
-      <c r="D69" t="str">
-        <v>불량</v>
-      </c>
-      <c r="E69" t="str">
-        <v>양호</v>
-      </c>
-      <c r="F69" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G69" t="str">
-        <v>10.3</v>
-      </c>
-      <c r="H69" t="str">
-        <v>22년07월_최초발생</v>
-      </c>
-      <c r="I69" t="str">
-        <v>9</v>
-      </c>
-      <c r="J69" t="str">
-        <v>0</v>
-      </c>
-      <c r="K69" t="str">
-        <v>0</v>
-      </c>
-      <c r="L69" t="str">
-        <v>1</v>
-      </c>
-      <c r="M69" t="str">
-        <v>0</v>
-      </c>
-      <c r="N69" t="str">
-        <v>10</v>
-      </c>
-      <c r="O69" t="str">
-        <v>긴급</v>
-      </c>
-      <c r="P69" t="str">
-        <v>10cm이상 보도침하</v>
-      </c>
-      <c r="Q69" t="str">
-        <v>이의동421-5</v>
-      </c>
-      <c r="R69" t="str">
-        <v/>
-      </c>
-      <c r="S69" t="str">
-        <v>입출고선환기구 옆 보도</v>
-      </c>
-      <c r="T69" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>26-25</v>
-      </c>
-      <c r="B70" t="str">
-        <v>광교로</v>
-      </c>
-      <c r="C70" t="str">
-        <v>26-수원시-25</v>
-      </c>
-      <c r="D70" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E70" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F70" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G70" t="str">
-        <v>10.3</v>
-      </c>
-      <c r="H70" t="str">
-        <v>-</v>
-      </c>
-      <c r="I70" t="str">
-        <v>0</v>
-      </c>
-      <c r="J70" t="str">
-        <v>3</v>
-      </c>
-      <c r="K70" t="str">
-        <v>0</v>
-      </c>
-      <c r="L70" t="str">
-        <v>1</v>
-      </c>
-      <c r="M70" t="str">
-        <v>0</v>
-      </c>
-      <c r="N70" t="str">
-        <v>4</v>
-      </c>
-      <c r="O70" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P70" t="str">
-        <v>-</v>
-      </c>
-      <c r="Q70" t="str">
-        <v>이의동421-5</v>
-      </c>
-      <c r="R70" t="str">
-        <v/>
-      </c>
-      <c r="S70" t="str">
-        <v>입출고선환기구 옆 도로</v>
-      </c>
-      <c r="T70" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>26-26</v>
-      </c>
-      <c r="B71" t="str">
-        <v>광교로</v>
-      </c>
-      <c r="C71" t="str">
-        <v>26-수원시-26</v>
-      </c>
-      <c r="D71" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E71" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F71" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G71" t="str">
-        <v>10.3</v>
-      </c>
-      <c r="H71" t="str">
-        <v>-</v>
-      </c>
-      <c r="I71" t="str">
-        <v>0</v>
-      </c>
-      <c r="J71" t="str">
-        <v>3</v>
-      </c>
-      <c r="K71" t="str">
-        <v>0</v>
-      </c>
-      <c r="L71" t="str">
-        <v>1</v>
-      </c>
-      <c r="M71" t="str">
-        <v>0</v>
-      </c>
-      <c r="N71" t="str">
-        <v>4</v>
-      </c>
-      <c r="O71" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P71" t="str">
-        <v>-</v>
-      </c>
-      <c r="Q71" t="str">
-        <v>이의동1322-2</v>
-      </c>
-      <c r="R71" t="str">
-        <v/>
-      </c>
-      <c r="S71" t="str">
-        <v>광교사거리 전 도로</v>
-      </c>
-      <c r="T71" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T71"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T68"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-수원시-보고서.xlsx
+++ b/25-경기철도-수원시-보고서.xlsx
@@ -4508,7 +4508,7 @@
         <v/>
       </c>
       <c r="S69" t="str">
-        <v>자연자연앤 힐스테이트 자이언트리딩 / 하선시점 피난계단 뒤 보도(도청로65)</v>
+        <v>자연앤 힐스테이트 자이언트리딩 / 하선시점 피난계단 뒤 보도(도청로65)</v>
       </c>
       <c r="T69" t="str">
         <v>현장확인필요</v>

--- a/25-경기철도-수원시-보고서.xlsx
+++ b/25-경기철도-수원시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T69"/>
+  <dimension ref="A1:T68"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,13 +485,13 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-수원시-2</v>
+        <v>25-수원시-3</v>
       </c>
       <c r="D5" t="str">
         <v>양호</v>
@@ -533,13 +533,13 @@
         <v/>
       </c>
       <c r="Q5" t="str">
-        <v>영통구 하동 968-4</v>
+        <v>법조타운 사거리</v>
       </c>
       <c r="R5" t="str">
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>아름드리동물병원 앞 삼차로 도로</v>
+        <v>범조타운 사거리 도로</v>
       </c>
       <c r="T5" t="str">
         <v/>
@@ -547,13 +547,13 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C6" t="str">
-        <v>25-수원시-3</v>
+        <v>25-수원시-4</v>
       </c>
       <c r="D6" t="str">
         <v>양호</v>
@@ -595,13 +595,13 @@
         <v/>
       </c>
       <c r="Q6" t="str">
-        <v>법조타운 사거리</v>
+        <v>영통구 이의동 1381-24</v>
       </c>
       <c r="R6" t="str">
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>범조타운 사거리 도로</v>
+        <v>용인서울고속도로 밑 도로</v>
       </c>
       <c r="T6" t="str">
         <v/>
@@ -609,19 +609,19 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C7" t="str">
-        <v>25-수원시-4</v>
+        <v>25-수원시-5</v>
       </c>
       <c r="D7" t="str">
         <v>양호</v>
       </c>
       <c r="E7" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F7" t="str">
         <v>건조</v>
@@ -636,7 +636,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O7" t="str">
         <v>일반</v>
@@ -657,13 +657,13 @@
         <v/>
       </c>
       <c r="Q7" t="str">
-        <v>영통구 이의동 1381-24</v>
+        <v>이의동 1381-25</v>
       </c>
       <c r="R7" t="str">
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>용인서울고속도로 밑 도로</v>
+        <v>용인서울고속도로 밑 통로 앞 도로</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -671,19 +671,19 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C8" t="str">
-        <v>25-수원시-5</v>
+        <v>25-수원시-6</v>
       </c>
       <c r="D8" t="str">
         <v>양호</v>
       </c>
       <c r="E8" t="str">
-        <v>종균열</v>
+        <v>-</v>
       </c>
       <c r="F8" t="str">
         <v>건조</v>
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -710,22 +710,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="str">
         <v>일반</v>
       </c>
       <c r="P8" t="str">
-        <v/>
+        <v>보도침하 5cm미만</v>
       </c>
       <c r="Q8" t="str">
-        <v>이의동 1381-25</v>
+        <v>이의동 1304-2</v>
       </c>
       <c r="R8" t="str">
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>용인서울고속도로 밑 통로 앞 도로</v>
+        <v>본선환기구 #2-14 피난계단 앞 보도</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -733,19 +733,19 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C9" t="str">
-        <v>25-수원시-6</v>
+        <v>25-수원시-7</v>
       </c>
       <c r="D9" t="str">
         <v>양호</v>
       </c>
       <c r="E9" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F9" t="str">
         <v>건조</v>
@@ -760,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -772,22 +772,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O9" t="str">
         <v>일반</v>
       </c>
       <c r="P9" t="str">
-        <v>보도침하 5cm미만</v>
+        <v/>
       </c>
       <c r="Q9" t="str">
-        <v>이의동 1304-2</v>
+        <v>센트럴파크로 사거리</v>
       </c>
       <c r="R9" t="str">
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>본선환기구 #2-14 피난계단 앞 보도</v>
+        <v>센트럴파크로 사거리 도로</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -795,13 +795,13 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C10" t="str">
-        <v>25-수원시-7</v>
+        <v>25-수원시-8</v>
       </c>
       <c r="D10" t="str">
         <v>양호</v>
@@ -843,13 +843,13 @@
         <v/>
       </c>
       <c r="Q10" t="str">
-        <v>센트럴파크로 사거리</v>
+        <v>영통구 하동 1015</v>
       </c>
       <c r="R10" t="str">
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>센트럴파크로 사거리 도로</v>
+        <v>비치맨션 앞 도로</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -857,13 +857,13 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C11" t="str">
-        <v>25-수원시-8</v>
+        <v>25-수원시-9</v>
       </c>
       <c r="D11" t="str">
         <v>양호</v>
@@ -905,13 +905,13 @@
         <v/>
       </c>
       <c r="Q11" t="str">
-        <v>영통구 하동 1015</v>
+        <v>영통구 하동 1016</v>
       </c>
       <c r="R11" t="str">
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>비치맨션 앞 도로</v>
+        <v>영통찌개지존 앞 도로</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -919,19 +919,19 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C12" t="str">
-        <v>25-수원시-9</v>
+        <v>25-수원시-10</v>
       </c>
       <c r="D12" t="str">
         <v>양호</v>
       </c>
       <c r="E12" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F12" t="str">
         <v>건조</v>
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O12" t="str">
         <v>일반</v>
       </c>
       <c r="P12" t="str">
-        <v/>
+        <v>보도침하 5cm미만</v>
       </c>
       <c r="Q12" t="str">
-        <v>영통구 하동 1016</v>
+        <v>영통구 하동 1016-1</v>
       </c>
       <c r="R12" t="str">
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>영통찌개지존 앞 도로</v>
+        <v>호랭이전골 앞 보도</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -981,19 +981,19 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C13" t="str">
-        <v>25-수원시-10</v>
+        <v>25-수원시-11</v>
       </c>
       <c r="D13" t="str">
         <v>양호</v>
       </c>
       <c r="E13" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F13" t="str">
         <v>건조</v>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1020,22 +1020,22 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O13" t="str">
         <v>일반</v>
       </c>
       <c r="P13" t="str">
-        <v>보도침하 5cm미만</v>
+        <v/>
       </c>
       <c r="Q13" t="str">
-        <v>영통구 하동 1016-1</v>
+        <v>컨벤션센터 사거리</v>
       </c>
       <c r="R13" t="str">
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>호랭이전골 앞 보도</v>
+        <v>컨벤션센터 사거리 도로</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1043,13 +1043,13 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C14" t="str">
-        <v>25-수원시-11</v>
+        <v>25-수원시-12</v>
       </c>
       <c r="D14" t="str">
         <v>양호</v>
@@ -1091,13 +1091,13 @@
         <v/>
       </c>
       <c r="Q14" t="str">
-        <v>컨벤션센터 사거리</v>
+        <v>영통구 하동 1017-9</v>
       </c>
       <c r="R14" t="str">
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>컨벤션센터 사거리 도로</v>
+        <v>수원컨벤션센터 앞 도로</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1105,19 +1105,19 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C15" t="str">
-        <v>25-수원시-12</v>
+        <v>25-수원시-13</v>
       </c>
       <c r="D15" t="str">
         <v>양호</v>
       </c>
       <c r="E15" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F15" t="str">
         <v>건조</v>
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1144,22 +1144,22 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O15" t="str">
         <v>일반</v>
       </c>
       <c r="P15" t="str">
-        <v/>
+        <v>보도침하 5cm미만</v>
       </c>
       <c r="Q15" t="str">
-        <v>영통구 하동 1017-9</v>
+        <v>이의동 1337</v>
       </c>
       <c r="R15" t="str">
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>수원컨벤션센터 앞 도로</v>
+        <v>롯데몰 앞 보도</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -1167,19 +1167,19 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C16" t="str">
-        <v>25-수원시-13</v>
+        <v>25-수원시-14</v>
       </c>
       <c r="D16" t="str">
         <v>양호</v>
       </c>
       <c r="E16" t="str">
-        <v>-</v>
+        <v>횡균열</v>
       </c>
       <c r="F16" t="str">
         <v>건조</v>
@@ -1194,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -1206,22 +1206,22 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="str">
         <v>일반</v>
       </c>
       <c r="P16" t="str">
-        <v>보도침하 5cm미만</v>
+        <v/>
       </c>
       <c r="Q16" t="str">
-        <v>이의동 1337</v>
+        <v>이의동 1338</v>
       </c>
       <c r="R16" t="str">
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>롯데몰 앞 보도</v>
+        <v>롯데몰 앞 도로</v>
       </c>
       <c r="T16" t="str">
         <v/>
@@ -1229,19 +1229,19 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" t="str">
-        <v>광교중앙로</v>
+        <v>도청로</v>
       </c>
       <c r="C17" t="str">
-        <v>25-수원시-14</v>
+        <v>25-수원시-15</v>
       </c>
       <c r="D17" t="str">
         <v>양호</v>
       </c>
       <c r="E17" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F17" t="str">
         <v>건조</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O17" t="str">
         <v>일반</v>
@@ -1283,7 +1283,7 @@
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>롯데몰 앞 도로</v>
+        <v>광교센트럴 푸르지오시티 오피스텔 전용주차장 입구 도로</v>
       </c>
       <c r="T17" t="str">
         <v/>
@@ -1291,13 +1291,13 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" t="str">
         <v>도청로</v>
       </c>
       <c r="C18" t="str">
-        <v>25-수원시-15</v>
+        <v>25-수원시-16</v>
       </c>
       <c r="D18" t="str">
         <v>양호</v>
@@ -1339,13 +1339,13 @@
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v>이의동 1338</v>
+        <v>도청사거리</v>
       </c>
       <c r="R18" t="str">
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>광교센트럴 푸르지오시티 오피스텔 전용주차장 입구 도로</v>
+        <v>도청사거리 도로</v>
       </c>
       <c r="T18" t="str">
         <v/>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19" t="str">
         <v>도청로</v>
       </c>
       <c r="C19" t="str">
-        <v>25-수원시-16</v>
+        <v>25-수원시-17</v>
       </c>
       <c r="D19" t="str">
         <v>양호</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="Q19" t="str">
-        <v>도청사거리</v>
+        <v>영통구 이의동 1342</v>
       </c>
       <c r="R19" t="str">
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>도청사거리 도로</v>
+        <v>광교 청소년수련관 맞음편 도로</v>
       </c>
       <c r="T19" t="str">
         <v/>
@@ -1415,13 +1415,13 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" t="str">
         <v>도청로</v>
       </c>
       <c r="C20" t="str">
-        <v>25-수원시-17</v>
+        <v>25-수원시-18</v>
       </c>
       <c r="D20" t="str">
         <v>양호</v>
@@ -1463,13 +1463,13 @@
         <v/>
       </c>
       <c r="Q20" t="str">
-        <v>영통구 이의동 1342</v>
+        <v>이의동 262-7</v>
       </c>
       <c r="R20" t="str">
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>광교 청소년수련관 맞음편 도로</v>
+        <v>자연 앤 힐스테이트 입구 맞음편 도로</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -1477,13 +1477,13 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" t="str">
         <v>도청로</v>
       </c>
       <c r="C21" t="str">
-        <v>25-수원시-18</v>
+        <v>25-수원시-19</v>
       </c>
       <c r="D21" t="str">
         <v>양호</v>
@@ -1525,13 +1525,13 @@
         <v/>
       </c>
       <c r="Q21" t="str">
-        <v>이의동 262-7</v>
+        <v>영통구 이의동 0</v>
       </c>
       <c r="R21" t="str">
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>자연 앤 힐스테이트 입구 맞음편 도로</v>
+        <v>경기도서관 앞 도로</v>
       </c>
       <c r="T21" t="str">
         <v/>
@@ -1539,19 +1539,19 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" t="str">
         <v>도청로</v>
       </c>
       <c r="C22" t="str">
-        <v>25-수원시-19</v>
+        <v>25-수원시-20</v>
       </c>
       <c r="D22" t="str">
         <v>양호</v>
       </c>
       <c r="E22" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F22" t="str">
         <v>건조</v>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1578,22 +1578,22 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="str">
         <v>일반</v>
       </c>
       <c r="P22" t="str">
-        <v/>
+        <v>보도침하 9cm(보도판석 파손 동반)</v>
       </c>
       <c r="Q22" t="str">
-        <v>영통구 이의동 0</v>
+        <v>이의동 1344</v>
       </c>
       <c r="R22" t="str">
         <v/>
       </c>
       <c r="S22" t="str">
-        <v>경기도서관 앞 도로</v>
+        <v>광교중앙역 하선 피난계단 뒤 보도</v>
       </c>
       <c r="T22" t="str">
         <v/>
@@ -1601,19 +1601,19 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" t="str">
         <v>도청로</v>
       </c>
       <c r="C23" t="str">
-        <v>25-수원시-20</v>
+        <v>25-수원시-21</v>
       </c>
       <c r="D23" t="str">
         <v>양호</v>
       </c>
       <c r="E23" t="str">
-        <v>-</v>
+        <v>횡균열</v>
       </c>
       <c r="F23" t="str">
         <v>건조</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1640,22 +1640,22 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="str">
         <v>일반</v>
       </c>
       <c r="P23" t="str">
-        <v>보도침하 9cm(보도판석 파손 동반)</v>
+        <v/>
       </c>
       <c r="Q23" t="str">
-        <v>이의동 1344</v>
+        <v>이의동 1332</v>
       </c>
       <c r="R23" t="str">
         <v/>
       </c>
       <c r="S23" t="str">
-        <v>광교중앙역 하선 피난계단 뒤 보도</v>
+        <v>롯데마트 앞 양차선 도로</v>
       </c>
       <c r="T23" t="str">
         <v/>
@@ -1663,19 +1663,19 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" t="str">
         <v>도청로</v>
       </c>
       <c r="C24" t="str">
-        <v>25-수원시-21</v>
+        <v>25-수원시-22</v>
       </c>
       <c r="D24" t="str">
         <v>양호</v>
       </c>
       <c r="E24" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F24" t="str">
         <v>건조</v>
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -1702,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O24" t="str">
         <v>일반</v>
@@ -1717,7 +1717,7 @@
         <v/>
       </c>
       <c r="S24" t="str">
-        <v>롯데마트 앞 양차선 도로</v>
+        <v>버거킹 맞음편 도로</v>
       </c>
       <c r="T24" t="str">
         <v/>
@@ -1725,13 +1725,13 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" t="str">
         <v>도청로</v>
       </c>
       <c r="C25" t="str">
-        <v>25-수원시-22</v>
+        <v>25-수원시-23</v>
       </c>
       <c r="D25" t="str">
         <v>양호</v>
@@ -1773,13 +1773,13 @@
         <v/>
       </c>
       <c r="Q25" t="str">
-        <v>이의동 1332</v>
+        <v>광교고사거리</v>
       </c>
       <c r="R25" t="str">
         <v/>
       </c>
       <c r="S25" t="str">
-        <v>버거킹 맞음편 도로</v>
+        <v>광교고 사거리 도로</v>
       </c>
       <c r="T25" t="str">
         <v/>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26" t="str">
         <v>도청로</v>
       </c>
       <c r="C26" t="str">
-        <v>25-수원시-23</v>
+        <v>25-수원시-24</v>
       </c>
       <c r="D26" t="str">
         <v>양호</v>
@@ -1835,13 +1835,13 @@
         <v/>
       </c>
       <c r="Q26" t="str">
-        <v>광교고사거리</v>
+        <v>이의동 1331</v>
       </c>
       <c r="R26" t="str">
         <v/>
       </c>
       <c r="S26" t="str">
-        <v>광교고 사거리 도로</v>
+        <v>서브웨이 앞 양차선 도로</v>
       </c>
       <c r="T26" t="str">
         <v/>
@@ -1849,13 +1849,13 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" t="str">
-        <v>도청로</v>
+        <v>광교로</v>
       </c>
       <c r="C27" t="str">
-        <v>25-수원시-24</v>
+        <v>25-수원시-25</v>
       </c>
       <c r="D27" t="str">
         <v>양호</v>
@@ -1897,13 +1897,13 @@
         <v/>
       </c>
       <c r="Q27" t="str">
-        <v>이의동 1331</v>
+        <v>이의동 885-1</v>
       </c>
       <c r="R27" t="str">
         <v/>
       </c>
       <c r="S27" t="str">
-        <v>서브웨이 앞 양차선 도로</v>
+        <v>차세대 융합기술연구원 앞 도로</v>
       </c>
       <c r="T27" t="str">
         <v/>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28" t="str">
         <v>광교로</v>
       </c>
       <c r="C28" t="str">
-        <v>25-수원시-25</v>
+        <v>25-수원시-26</v>
       </c>
       <c r="D28" t="str">
         <v>양호</v>
@@ -1956,16 +1956,16 @@
         <v>일반</v>
       </c>
       <c r="P28" t="str">
-        <v/>
+        <v>보도침하 4cm</v>
       </c>
       <c r="Q28" t="str">
-        <v>이의동 885-1</v>
+        <v>이의동 884</v>
       </c>
       <c r="R28" t="str">
         <v/>
       </c>
       <c r="S28" t="str">
-        <v>차세대 융합기술연구원 앞 도로</v>
+        <v>차세대 융합기술연구원 버스정류장 보도</v>
       </c>
       <c r="T28" t="str">
         <v/>
@@ -1973,13 +1973,13 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29" t="str">
         <v>광교로</v>
       </c>
       <c r="C29" t="str">
-        <v>25-수원시-26</v>
+        <v>25-수원시-27</v>
       </c>
       <c r="D29" t="str">
         <v>양호</v>
@@ -2018,16 +2018,16 @@
         <v>일반</v>
       </c>
       <c r="P29" t="str">
-        <v>보도침하 4cm</v>
+        <v/>
       </c>
       <c r="Q29" t="str">
-        <v>이의동 884</v>
+        <v>이의동 1381-27</v>
       </c>
       <c r="R29" t="str">
         <v/>
       </c>
       <c r="S29" t="str">
-        <v>차세대 융합기술연구원 버스정류장 보도</v>
+        <v>차세대 융합기술연구원 버스정류장 도로</v>
       </c>
       <c r="T29" t="str">
         <v/>
@@ -2035,13 +2035,13 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B30" t="str">
         <v>광교로</v>
       </c>
       <c r="C30" t="str">
-        <v>25-수원시-27</v>
+        <v>25-수원시-28</v>
       </c>
       <c r="D30" t="str">
         <v>양호</v>
@@ -2083,13 +2083,13 @@
         <v/>
       </c>
       <c r="Q30" t="str">
-        <v>이의동 1381-27</v>
+        <v>이의동 1329</v>
       </c>
       <c r="R30" t="str">
         <v/>
       </c>
       <c r="S30" t="str">
-        <v>차세대 융합기술연구원 버스정류장 도로</v>
+        <v>새마을금고 앞 도로</v>
       </c>
       <c r="T30" t="str">
         <v/>
@@ -2097,13 +2097,13 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31" t="str">
         <v>광교로</v>
       </c>
       <c r="C31" t="str">
-        <v>25-수원시-28</v>
+        <v>25-수원시-29</v>
       </c>
       <c r="D31" t="str">
         <v>양호</v>
@@ -2145,13 +2145,13 @@
         <v/>
       </c>
       <c r="Q31" t="str">
-        <v>이의동 1329</v>
+        <v>이의동 884</v>
       </c>
       <c r="R31" t="str">
         <v/>
       </c>
       <c r="S31" t="str">
-        <v>새마을금고 앞 도로</v>
+        <v>가로등(광교로121-수원43) 도로</v>
       </c>
       <c r="T31" t="str">
         <v/>
@@ -2159,19 +2159,19 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32" t="str">
         <v>광교로</v>
       </c>
       <c r="C32" t="str">
-        <v>25-수원시-29</v>
+        <v>25-수원시-30</v>
       </c>
       <c r="D32" t="str">
         <v>양호</v>
       </c>
       <c r="E32" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F32" t="str">
         <v>건조</v>
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O32" t="str">
         <v>일반</v>
@@ -2207,13 +2207,13 @@
         <v/>
       </c>
       <c r="Q32" t="str">
-        <v>이의동 884</v>
+        <v>이의동 1322-1</v>
       </c>
       <c r="R32" t="str">
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>가로등(광교로121-수원43) 도로</v>
+        <v>광교비스니스센터 앞 도로</v>
       </c>
       <c r="T32" t="str">
         <v/>
@@ -2221,19 +2221,19 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33" t="str">
         <v>광교로</v>
       </c>
       <c r="C33" t="str">
-        <v>25-수원시-30</v>
+        <v>25-수원시-31</v>
       </c>
       <c r="D33" t="str">
-        <v>양호</v>
+        <v>보통</v>
       </c>
       <c r="E33" t="str">
-        <v>종균열</v>
+        <v>-</v>
       </c>
       <c r="F33" t="str">
         <v>건조</v>
@@ -2245,10 +2245,10 @@
         <v>-</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -2260,22 +2260,22 @@
         <v>0</v>
       </c>
       <c r="N33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O33" t="str">
         <v>일반</v>
       </c>
       <c r="P33" t="str">
-        <v/>
+        <v>보도침하(5~10cm, '22.07월 최초발생)</v>
       </c>
       <c r="Q33" t="str">
-        <v>이의동 1322-1</v>
+        <v>이의동 421-5</v>
       </c>
       <c r="R33" t="str">
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>광교비스니스센터 앞 도로</v>
+        <v>입출고선 환기구 옆 보도</v>
       </c>
       <c r="T33" t="str">
         <v/>
@@ -2283,19 +2283,19 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34" t="str">
         <v>광교로</v>
       </c>
       <c r="C34" t="str">
-        <v>25-수원시-31</v>
+        <v>25-수원시-32</v>
       </c>
       <c r="D34" t="str">
-        <v>보통</v>
+        <v>양호</v>
       </c>
       <c r="E34" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F34" t="str">
         <v>건조</v>
@@ -2307,10 +2307,10 @@
         <v>-</v>
       </c>
       <c r="I34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -2328,7 +2328,7 @@
         <v>일반</v>
       </c>
       <c r="P34" t="str">
-        <v>보도침하(5~10cm, '22.07월 최초발생)</v>
+        <v/>
       </c>
       <c r="Q34" t="str">
         <v>이의동 421-5</v>
@@ -2337,7 +2337,7 @@
         <v/>
       </c>
       <c r="S34" t="str">
-        <v>입출고선 환기구 옆 보도</v>
+        <v>입출고선 환기구 옆 도로</v>
       </c>
       <c r="T34" t="str">
         <v/>
@@ -2345,19 +2345,19 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35" t="str">
         <v>광교로</v>
       </c>
       <c r="C35" t="str">
-        <v>25-수원시-32</v>
+        <v>25-수원시-33</v>
       </c>
       <c r="D35" t="str">
-        <v>양호</v>
+        <v>보통</v>
       </c>
       <c r="E35" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F35" t="str">
         <v>건조</v>
@@ -2369,10 +2369,10 @@
         <v>-</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -2384,13 +2384,13 @@
         <v>0</v>
       </c>
       <c r="N35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O35" t="str">
         <v>일반</v>
       </c>
       <c r="P35" t="str">
-        <v/>
+        <v>L형측구침하 7cm(측구 파손 동반)</v>
       </c>
       <c r="Q35" t="str">
         <v>이의동 421-5</v>
@@ -2399,7 +2399,7 @@
         <v/>
       </c>
       <c r="S35" t="str">
-        <v>입출고선 환기구 옆 도로</v>
+        <v>입출고선 환기구 앞 도로</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -2407,19 +2407,19 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B36" t="str">
         <v>광교로</v>
       </c>
       <c r="C36" t="str">
-        <v>25-수원시-33</v>
+        <v>25-수원시-34</v>
       </c>
       <c r="D36" t="str">
-        <v>보통</v>
+        <v>양호</v>
       </c>
       <c r="E36" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F36" t="str">
         <v>건조</v>
@@ -2431,10 +2431,10 @@
         <v>-</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -2446,22 +2446,22 @@
         <v>0</v>
       </c>
       <c r="N36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O36" t="str">
         <v>일반</v>
       </c>
       <c r="P36" t="str">
-        <v>L형측구침하 7cm(측구 파손 동반)</v>
+        <v/>
       </c>
       <c r="Q36" t="str">
-        <v>이의동 421-5</v>
+        <v>이의동 835</v>
       </c>
       <c r="R36" t="str">
         <v/>
       </c>
       <c r="S36" t="str">
-        <v>입출고선 환기구 앞 도로</v>
+        <v>맥도날드 앞 양차선 도로</v>
       </c>
       <c r="T36" t="str">
         <v/>
@@ -2469,13 +2469,13 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B37" t="str">
-        <v>광교로</v>
+        <v>창룡대로</v>
       </c>
       <c r="C37" t="str">
-        <v>25-수원시-34</v>
+        <v>25-수원시-35</v>
       </c>
       <c r="D37" t="str">
         <v>양호</v>
@@ -2517,13 +2517,13 @@
         <v/>
       </c>
       <c r="Q37" t="str">
-        <v>이의동 835</v>
+        <v>광교사거리</v>
       </c>
       <c r="R37" t="str">
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>맥도날드 앞 양차선 도로</v>
+        <v>광교사거리 도로</v>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -2531,19 +2531,19 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B38" t="str">
         <v>창룡대로</v>
       </c>
       <c r="C38" t="str">
-        <v>25-수원시-35</v>
+        <v>25-수원시-36</v>
       </c>
       <c r="D38" t="str">
         <v>양호</v>
       </c>
       <c r="E38" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F38" t="str">
         <v>건조</v>
@@ -2558,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -2570,22 +2570,22 @@
         <v>0</v>
       </c>
       <c r="N38">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O38" t="str">
         <v>일반</v>
       </c>
       <c r="P38" t="str">
-        <v/>
+        <v>침하 5cm미만(종방향, 진행성 우려)</v>
       </c>
       <c r="Q38" t="str">
-        <v>광교사거리</v>
+        <v>이의동 1379-7</v>
       </c>
       <c r="R38" t="str">
         <v/>
       </c>
       <c r="S38" t="str">
-        <v>광교사거리 도로</v>
+        <v>광교역사공원 앞 도로</v>
       </c>
       <c r="T38" t="str">
         <v/>
@@ -2593,19 +2593,19 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B39" t="str">
-        <v>창룡대로</v>
+        <v>광교로</v>
       </c>
       <c r="C39" t="str">
-        <v>25-수원시-36</v>
+        <v>25-수원시-37</v>
       </c>
       <c r="D39" t="str">
         <v>양호</v>
       </c>
       <c r="E39" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F39" t="str">
         <v>건조</v>
@@ -2620,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -2632,22 +2632,22 @@
         <v>0</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O39" t="str">
         <v>일반</v>
       </c>
       <c r="P39" t="str">
-        <v>침하 5cm미만(종방향, 진행성 우려)</v>
+        <v>침하 5cm미만</v>
       </c>
       <c r="Q39" t="str">
-        <v>이의동 1379-7</v>
+        <v>이의동 432-1</v>
       </c>
       <c r="R39" t="str">
         <v/>
       </c>
       <c r="S39" t="str">
-        <v>광교역사공원 앞 도로</v>
+        <v>GS칼텍스 LPG 앞 도로 양차선</v>
       </c>
       <c r="T39" t="str">
         <v/>
@@ -2655,13 +2655,13 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" t="str">
         <v>광교로</v>
       </c>
       <c r="C40" t="str">
-        <v>25-수원시-37</v>
+        <v>25-수원시-38</v>
       </c>
       <c r="D40" t="str">
         <v>양호</v>
@@ -2703,13 +2703,13 @@
         <v>침하 5cm미만</v>
       </c>
       <c r="Q40" t="str">
-        <v>이의동 432-1</v>
+        <v>이의동 433</v>
       </c>
       <c r="R40" t="str">
         <v/>
       </c>
       <c r="S40" t="str">
-        <v>GS칼텍스 LPG 앞 도로 양차선</v>
+        <v>수원광교박물관 전용주차장 앞 도로</v>
       </c>
       <c r="T40" t="str">
         <v/>
@@ -2717,13 +2717,13 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B41" t="str">
         <v>광교로</v>
       </c>
       <c r="C41" t="str">
-        <v>25-수원시-38</v>
+        <v>25-수원시-39</v>
       </c>
       <c r="D41" t="str">
         <v>양호</v>
@@ -2762,7 +2762,7 @@
         <v>일반</v>
       </c>
       <c r="P41" t="str">
-        <v>침하 5cm미만</v>
+        <v/>
       </c>
       <c r="Q41" t="str">
         <v>이의동 433</v>
@@ -2771,7 +2771,7 @@
         <v/>
       </c>
       <c r="S41" t="str">
-        <v>수원광교박물관 전용주차장 앞 도로</v>
+        <v>수원광교박물관 전용주차장 입구 앞 도로</v>
       </c>
       <c r="T41" t="str">
         <v/>
@@ -2779,19 +2779,19 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B42" t="str">
         <v>광교로</v>
       </c>
       <c r="C42" t="str">
-        <v>25-수원시-39</v>
+        <v>25-수원시-40</v>
       </c>
       <c r="D42" t="str">
         <v>양호</v>
       </c>
       <c r="E42" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F42" t="str">
         <v>건조</v>
@@ -2806,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -2818,42 +2818,43 @@
         <v>0</v>
       </c>
       <c r="N42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O42" t="str">
         <v>일반</v>
       </c>
       <c r="P42" t="str">
-        <v/>
+        <v>침하 5cm미만</v>
       </c>
       <c r="Q42" t="str">
-        <v>이의동 433</v>
+        <v>역사공원삼거리</v>
       </c>
       <c r="R42" t="str">
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>수원광교박물관 전용주차장 입구 앞 도로</v>
+        <v>역사공원 삼거리 도로</v>
       </c>
       <c r="T42" t="str">
         <v/>
       </c>
     </row>
-    <row r="43">
+    <row r="43" xml:space="preserve">
       <c r="A43">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B43" t="str">
         <v>광교로</v>
       </c>
       <c r="C43" t="str">
-        <v>25-수원시-40</v>
+        <v>25-수원시-41</v>
       </c>
       <c r="D43" t="str">
         <v>양호</v>
       </c>
-      <c r="E43" t="str">
-        <v>횡균열</v>
+      <c r="E43" t="str" xml:space="preserve">
+        <v xml:space="preserve">종균열_x000d_
+횡균열</v>
       </c>
       <c r="F43" t="str">
         <v>건조</v>
@@ -2886,7 +2887,7 @@
         <v>일반</v>
       </c>
       <c r="P43" t="str">
-        <v>침하 5cm미만</v>
+        <v/>
       </c>
       <c r="Q43" t="str">
         <v>역사공원삼거리</v>
@@ -2901,64 +2902,63 @@
         <v/>
       </c>
     </row>
-    <row r="44" xml:space="preserve">
-      <c r="A44">
-        <v>41</v>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>26-01</v>
       </c>
       <c r="B44" t="str">
-        <v>광교로</v>
+        <v>광교중앙로</v>
       </c>
       <c r="C44" t="str">
-        <v>25-수원시-41</v>
+        <v>26-수원시-01</v>
       </c>
       <c r="D44" t="str">
         <v>양호</v>
       </c>
-      <c r="E44" t="str" xml:space="preserve">
-        <v xml:space="preserve">종균열_x000d_
-횡균열</v>
+      <c r="E44" t="str">
+        <v>횡균열</v>
       </c>
       <c r="F44" t="str">
-        <v>건조</v>
+        <v>양호</v>
       </c>
       <c r="G44" t="str">
-        <v>9.3</v>
+        <v>10.3</v>
       </c>
       <c r="H44" t="str">
         <v>-</v>
       </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>1</v>
-      </c>
-      <c r="K44">
-        <v>0</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44">
-        <v>1</v>
+      <c r="I44" t="str">
+        <v>0</v>
+      </c>
+      <c r="J44" t="str">
+        <v>1</v>
+      </c>
+      <c r="K44" t="str">
+        <v>0</v>
+      </c>
+      <c r="L44" t="str">
+        <v>1</v>
+      </c>
+      <c r="M44" t="str">
+        <v>0</v>
+      </c>
+      <c r="N44" t="str">
+        <v>2</v>
       </c>
       <c r="O44" t="str">
         <v>일반</v>
       </c>
       <c r="P44" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="Q44" t="str">
-        <v>역사공원삼거리</v>
+        <v>하동147-115</v>
       </c>
       <c r="R44" t="str">
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>역사공원 삼거리 도로</v>
+        <v>진고개터널 앞 도로</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -2966,19 +2966,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>26-01</v>
+        <v>26-02</v>
       </c>
       <c r="B45" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C45" t="str">
-        <v>26-수원시-01</v>
+        <v>26-수원시-02</v>
       </c>
       <c r="D45" t="str">
         <v>양호</v>
       </c>
       <c r="E45" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F45" t="str">
         <v>양호</v>
@@ -3014,13 +3014,13 @@
         <v>-</v>
       </c>
       <c r="Q45" t="str">
-        <v>하동147-115</v>
+        <v>하동956</v>
       </c>
       <c r="R45" t="str">
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>진고개터널 앞 도로</v>
+        <v>광교호수마을휴먼시아3210동 버스정류장 앞 도로(광교중앙로247)</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -3028,19 +3028,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>26-02</v>
+        <v>26-03</v>
       </c>
       <c r="B46" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C46" t="str">
-        <v>26-수원시-02</v>
+        <v>26-수원시-03</v>
       </c>
       <c r="D46" t="str">
         <v>양호</v>
       </c>
       <c r="E46" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F46" t="str">
         <v>양호</v>
@@ -3055,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K46" t="str">
         <v>0</v>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O46" t="str">
         <v>일반</v>
@@ -3082,7 +3082,7 @@
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>광교호수마을휴먼시아3210동 버스정류장 앞 도로(광교중앙로247)</v>
+        <v>광교호수마을휴먼시아3201동 버스정류장 앞 도로(광교중앙로247)</v>
       </c>
       <c r="T46" t="str">
         <v/>
@@ -3090,19 +3090,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>26-03</v>
+        <v>26-04</v>
       </c>
       <c r="B47" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C47" t="str">
-        <v>26-수원시-03</v>
+        <v>26-수원시-04</v>
       </c>
       <c r="D47" t="str">
         <v>양호</v>
       </c>
       <c r="E47" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F47" t="str">
         <v>양호</v>
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K47" t="str">
         <v>0</v>
@@ -3129,7 +3129,7 @@
         <v>0</v>
       </c>
       <c r="N47" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O47" t="str">
         <v>일반</v>
@@ -3138,13 +3138,13 @@
         <v>-</v>
       </c>
       <c r="Q47" t="str">
-        <v>하동956</v>
+        <v>이의동1302-1</v>
       </c>
       <c r="R47" t="str">
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>광교호수마을휴먼시아3201동 버스정류장 앞 도로(광교중앙로247)</v>
+        <v>지하차도 앞</v>
       </c>
       <c r="T47" t="str">
         <v/>
@@ -3152,19 +3152,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>26-04</v>
+        <v>26-05</v>
       </c>
       <c r="B48" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C48" t="str">
-        <v>26-수원시-04</v>
+        <v>26-수원시-05</v>
       </c>
       <c r="D48" t="str">
         <v>양호</v>
       </c>
       <c r="E48" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F48" t="str">
         <v>양호</v>
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K48" t="str">
         <v>0</v>
@@ -3191,7 +3191,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O48" t="str">
         <v>일반</v>
@@ -3200,13 +3200,13 @@
         <v>-</v>
       </c>
       <c r="Q48" t="str">
-        <v>이의동1302-1</v>
+        <v>하동1013</v>
       </c>
       <c r="R48" t="str">
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>지하차도 앞</v>
+        <v>광교더리브아파트6209동 앞 도로(센트럴파크로34)</v>
       </c>
       <c r="T48" t="str">
         <v/>
@@ -3214,13 +3214,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>26-05</v>
+        <v>26-06</v>
       </c>
       <c r="B49" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C49" t="str">
-        <v>26-수원시-05</v>
+        <v>26-수원시-06</v>
       </c>
       <c r="D49" t="str">
         <v>양호</v>
@@ -3262,13 +3262,13 @@
         <v>-</v>
       </c>
       <c r="Q49" t="str">
-        <v>하동1013</v>
+        <v>이의동1334-1</v>
       </c>
       <c r="R49" t="str">
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>광교더리브아파트6209동 앞 도로(센트럴파크로34)</v>
+        <v>등포칼국수 건너편 도로</v>
       </c>
       <c r="T49" t="str">
         <v/>
@@ -3276,13 +3276,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>26-06</v>
+        <v>26-07</v>
       </c>
       <c r="B50" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C50" t="str">
-        <v>26-수원시-06</v>
+        <v>26-수원시-07</v>
       </c>
       <c r="D50" t="str">
         <v>양호</v>
@@ -3324,13 +3324,13 @@
         <v>-</v>
       </c>
       <c r="Q50" t="str">
-        <v>이의동1334-1</v>
+        <v>이의동1334</v>
       </c>
       <c r="R50" t="str">
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>등포칼국수 건너편 도로</v>
+        <v>광교센트럴뷰아파트6013동 버스정류장 앞 도로(센트럴타운로22번길36)</v>
       </c>
       <c r="T50" t="str">
         <v/>
@@ -3338,19 +3338,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>26-07</v>
+        <v>26-08</v>
       </c>
       <c r="B51" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C51" t="str">
-        <v>26-수원시-07</v>
+        <v>26-수원시-08</v>
       </c>
       <c r="D51" t="str">
         <v>양호</v>
       </c>
       <c r="E51" t="str">
-        <v>거북등</v>
+        <v>종횡균열</v>
       </c>
       <c r="F51" t="str">
         <v>양호</v>
@@ -3365,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K51" t="str">
         <v>0</v>
@@ -3377,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="N51" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O51" t="str">
         <v>일반</v>
@@ -3386,13 +3386,13 @@
         <v>-</v>
       </c>
       <c r="Q51" t="str">
-        <v>이의동1334</v>
+        <v>이의동1334-3</v>
       </c>
       <c r="R51" t="str">
         <v/>
       </c>
       <c r="S51" t="str">
-        <v>광교센트럴뷰아파트6013동 버스정류장 앞 도로(센트럴타운로22번길36)</v>
+        <v>컨베션센터 사거리</v>
       </c>
       <c r="T51" t="str">
         <v/>
@@ -3400,19 +3400,19 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>26-08</v>
+        <v>26-09</v>
       </c>
       <c r="B52" t="str">
         <v>광교중앙로</v>
       </c>
       <c r="C52" t="str">
-        <v>26-수원시-08</v>
+        <v>26-수원시-09</v>
       </c>
       <c r="D52" t="str">
         <v>양호</v>
       </c>
       <c r="E52" t="str">
-        <v>종횡균열</v>
+        <v>양호</v>
       </c>
       <c r="F52" t="str">
         <v>양호</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="str">
         <v>0</v>
@@ -3439,22 +3439,22 @@
         <v>0</v>
       </c>
       <c r="N52" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O52" t="str">
         <v>일반</v>
       </c>
       <c r="P52" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q52" t="str">
-        <v>이의동1334-3</v>
+        <v>하동1017</v>
       </c>
       <c r="R52" t="str">
         <v/>
       </c>
       <c r="S52" t="str">
-        <v>컨베션센터 사거리</v>
+        <v>수원컨벤션센터 버스정류장 앞 도로(광교중앙로140)</v>
       </c>
       <c r="T52" t="str">
         <v/>
@@ -3462,19 +3462,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>26-09</v>
+        <v>26-10</v>
       </c>
       <c r="B53" t="str">
-        <v>광교중앙로</v>
+        <v>도청로</v>
       </c>
       <c r="C53" t="str">
-        <v>26-수원시-09</v>
+        <v>26-수원시-10</v>
       </c>
       <c r="D53" t="str">
         <v>양호</v>
       </c>
       <c r="E53" t="str">
-        <v>양호</v>
+        <v>거북등</v>
       </c>
       <c r="F53" t="str">
         <v>양호</v>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K53" t="str">
         <v>0</v>
@@ -3501,22 +3501,22 @@
         <v>0</v>
       </c>
       <c r="N53" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O53" t="str">
         <v>일반</v>
       </c>
       <c r="P53" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q53" t="str">
-        <v>하동1017</v>
+        <v>이의동1338</v>
       </c>
       <c r="R53" t="str">
         <v/>
       </c>
       <c r="S53" t="str">
-        <v>수원컨벤션센터 버스정류장 앞 도로(광교중앙로140)</v>
+        <v>롯데몰 주차장 출입로 앞 도로(도청로10)</v>
       </c>
       <c r="T53" t="str">
         <v/>
@@ -3524,13 +3524,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>26-10</v>
+        <v>26-11</v>
       </c>
       <c r="B54" t="str">
         <v>도청로</v>
       </c>
       <c r="C54" t="str">
-        <v>26-수원시-10</v>
+        <v>26-수원시-11</v>
       </c>
       <c r="D54" t="str">
         <v>양호</v>
@@ -3572,13 +3572,13 @@
         <v>-</v>
       </c>
       <c r="Q54" t="str">
-        <v>이의동1338</v>
+        <v>이의동198</v>
       </c>
       <c r="R54" t="str">
         <v/>
       </c>
       <c r="S54" t="str">
-        <v>롯데몰 주차장 출입로 앞 도로(도청로10)</v>
+        <v>도청사거리</v>
       </c>
       <c r="T54" t="str">
         <v/>
@@ -3586,19 +3586,19 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>26-11</v>
+        <v>26-12</v>
       </c>
       <c r="B55" t="str">
         <v>도청로</v>
       </c>
       <c r="C55" t="str">
-        <v>26-수원시-11</v>
+        <v>26-수원시-12</v>
       </c>
       <c r="D55" t="str">
         <v>양호</v>
       </c>
       <c r="E55" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F55" t="str">
         <v>양호</v>
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="J55" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K55" t="str">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="N55" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O55" t="str">
         <v>일반</v>
@@ -3634,13 +3634,13 @@
         <v>-</v>
       </c>
       <c r="Q55" t="str">
-        <v>이의동198</v>
+        <v>이의동262</v>
       </c>
       <c r="R55" t="str">
         <v/>
       </c>
       <c r="S55" t="str">
-        <v>도청사거리</v>
+        <v>경기도서관 주차장 입구 앞(도청로40)</v>
       </c>
       <c r="T55" t="str">
         <v/>
@@ -3648,19 +3648,19 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>26-12</v>
+        <v>26-13</v>
       </c>
       <c r="B56" t="str">
         <v>도청로</v>
       </c>
       <c r="C56" t="str">
-        <v>26-수원시-12</v>
+        <v>26-수원시-13</v>
       </c>
       <c r="D56" t="str">
         <v>양호</v>
       </c>
       <c r="E56" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F56" t="str">
         <v>양호</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K56" t="str">
         <v>0</v>
@@ -3687,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="N56" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O56" t="str">
         <v>일반</v>
@@ -3696,13 +3696,13 @@
         <v>-</v>
       </c>
       <c r="Q56" t="str">
-        <v>이의동262</v>
+        <v>이의동262-7</v>
       </c>
       <c r="R56" t="str">
         <v/>
       </c>
       <c r="S56" t="str">
-        <v>경기도서관 주차장 입구 앞(도청로40)</v>
+        <v>경기도서관 정문 앞 도로(도청로40)</v>
       </c>
       <c r="T56" t="str">
         <v/>
@@ -3710,19 +3710,19 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>26-13</v>
+        <v>26-16</v>
       </c>
       <c r="B57" t="str">
         <v>도청로</v>
       </c>
       <c r="C57" t="str">
-        <v>26-수원시-13</v>
+        <v>26-수원시-16</v>
       </c>
       <c r="D57" t="str">
         <v>양호</v>
       </c>
       <c r="E57" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F57" t="str">
         <v>양호</v>
@@ -3737,7 +3737,7 @@
         <v>0</v>
       </c>
       <c r="J57" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K57" t="str">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="N57" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O57" t="str">
         <v>일반</v>
@@ -3758,13 +3758,13 @@
         <v>-</v>
       </c>
       <c r="Q57" t="str">
-        <v>이의동262-7</v>
+        <v>이의동1332</v>
       </c>
       <c r="R57" t="str">
         <v/>
       </c>
       <c r="S57" t="str">
-        <v>경기도서관 정문 앞 도로(도청로40)</v>
+        <v>아브뉴프랑_광교점 아티제 앞 횡단보도(센트럴타운로85)</v>
       </c>
       <c r="T57" t="str">
         <v/>
@@ -3772,19 +3772,19 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>26-16</v>
+        <v>26-17</v>
       </c>
       <c r="B58" t="str">
         <v>도청로</v>
       </c>
       <c r="C58" t="str">
-        <v>26-수원시-16</v>
+        <v>26-수원시-17</v>
       </c>
       <c r="D58" t="str">
         <v>양호</v>
       </c>
       <c r="E58" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F58" t="str">
         <v>양호</v>
@@ -3799,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="J58" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K58" t="str">
         <v>0</v>
@@ -3811,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="N58" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O58" t="str">
         <v>일반</v>
@@ -3820,13 +3820,13 @@
         <v>-</v>
       </c>
       <c r="Q58" t="str">
-        <v>이의동1332</v>
+        <v>이의동1344</v>
       </c>
       <c r="R58" t="str">
         <v/>
       </c>
       <c r="S58" t="str">
-        <v>아브뉴프랑_광교점 아티제 앞 횡단보도(센트럴타운로85)</v>
+        <v>소중한집 인테리어_광교점 앞 도로(도청로65 상가1동)</v>
       </c>
       <c r="T58" t="str">
         <v/>
@@ -3834,13 +3834,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>26-17</v>
+        <v>26-18</v>
       </c>
       <c r="B59" t="str">
         <v>도청로</v>
       </c>
       <c r="C59" t="str">
-        <v>26-수원시-17</v>
+        <v>26-수원시-18</v>
       </c>
       <c r="D59" t="str">
         <v>양호</v>
@@ -3882,13 +3882,13 @@
         <v>-</v>
       </c>
       <c r="Q59" t="str">
-        <v>이의동1344</v>
+        <v>이의동1381-11</v>
       </c>
       <c r="R59" t="str">
         <v/>
       </c>
       <c r="S59" t="str">
-        <v>소중한집 인테리어_광교점 앞 도로(도청로65 상가1동)</v>
+        <v>광교고사거리</v>
       </c>
       <c r="T59" t="str">
         <v/>
@@ -3896,19 +3896,19 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>26-18</v>
+        <v>26-19</v>
       </c>
       <c r="B60" t="str">
-        <v>도청로</v>
+        <v>광교로</v>
       </c>
       <c r="C60" t="str">
-        <v>26-수원시-18</v>
+        <v>26-수원시-19</v>
       </c>
       <c r="D60" t="str">
         <v>양호</v>
       </c>
       <c r="E60" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F60" t="str">
         <v>양호</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="J60" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K60" t="str">
         <v>0</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="N60" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O60" t="str">
         <v>일반</v>
@@ -3944,13 +3944,13 @@
         <v>-</v>
       </c>
       <c r="Q60" t="str">
-        <v>이의동1381-11</v>
+        <v>이의동885-1</v>
       </c>
       <c r="R60" t="str">
         <v/>
       </c>
       <c r="S60" t="str">
-        <v>광교고사거리</v>
+        <v>차세대 융합기술연구원 앞 횡단보도</v>
       </c>
       <c r="T60" t="str">
         <v/>
@@ -3958,19 +3958,19 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>26-19</v>
+        <v>26-20</v>
       </c>
       <c r="B61" t="str">
         <v>광교로</v>
       </c>
       <c r="C61" t="str">
-        <v>26-수원시-19</v>
+        <v>26-수원시-20</v>
       </c>
       <c r="D61" t="str">
         <v>양호</v>
       </c>
       <c r="E61" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F61" t="str">
         <v>양호</v>
@@ -4006,13 +4006,13 @@
         <v>-</v>
       </c>
       <c r="Q61" t="str">
-        <v>이의동885-1</v>
+        <v>이의동1329</v>
       </c>
       <c r="R61" t="str">
         <v/>
       </c>
       <c r="S61" t="str">
-        <v>차세대 융합기술연구원 앞 횡단보도</v>
+        <v>안효빌딩 현대자동차 앞 도로(광교로146)</v>
       </c>
       <c r="T61" t="str">
         <v/>
@@ -4020,19 +4020,19 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>26-20</v>
+        <v>26-21</v>
       </c>
       <c r="B62" t="str">
         <v>광교로</v>
       </c>
       <c r="C62" t="str">
-        <v>26-수원시-20</v>
+        <v>26-수원시-21</v>
       </c>
       <c r="D62" t="str">
         <v>양호</v>
       </c>
       <c r="E62" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F62" t="str">
         <v>양호</v>
@@ -4047,7 +4047,7 @@
         <v>0</v>
       </c>
       <c r="J62" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K62" t="str">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="N62" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O62" t="str">
         <v>일반</v>
@@ -4068,13 +4068,13 @@
         <v>-</v>
       </c>
       <c r="Q62" t="str">
-        <v>이의동1329</v>
+        <v>이의동884</v>
       </c>
       <c r="R62" t="str">
         <v/>
       </c>
       <c r="S62" t="str">
-        <v>안효빌딩 현대자동차 앞 도로(광교로146)</v>
+        <v>차세대 융합기술연구원 버스정류장 앞 도로</v>
       </c>
       <c r="T62" t="str">
         <v/>
@@ -4082,19 +4082,19 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>26-21</v>
+        <v>26-22</v>
       </c>
       <c r="B63" t="str">
         <v>광교로</v>
       </c>
       <c r="C63" t="str">
-        <v>26-수원시-21</v>
+        <v>26-수원시-22</v>
       </c>
       <c r="D63" t="str">
         <v>양호</v>
       </c>
       <c r="E63" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F63" t="str">
         <v>양호</v>
@@ -4109,7 +4109,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K63" t="str">
         <v>0</v>
@@ -4121,7 +4121,7 @@
         <v>0</v>
       </c>
       <c r="N63" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O63" t="str">
         <v>일반</v>
@@ -4130,13 +4130,13 @@
         <v>-</v>
       </c>
       <c r="Q63" t="str">
-        <v>이의동884</v>
+        <v>이의동1322</v>
       </c>
       <c r="R63" t="str">
         <v/>
       </c>
       <c r="S63" t="str">
-        <v>차세대 융합기술연구원 버스정류장 앞 도로</v>
+        <v>광교 비지니스센터 앞 도로(광교로152))</v>
       </c>
       <c r="T63" t="str">
         <v/>
@@ -4144,19 +4144,19 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>26-22</v>
+        <v>26-23</v>
       </c>
       <c r="B64" t="str">
         <v>광교로</v>
       </c>
       <c r="C64" t="str">
-        <v>26-수원시-22</v>
+        <v>26-수원시-23</v>
       </c>
       <c r="D64" t="str">
-        <v>양호</v>
+        <v>불량</v>
       </c>
       <c r="E64" t="str">
-        <v>종균열</v>
+        <v>양호</v>
       </c>
       <c r="F64" t="str">
         <v>양호</v>
@@ -4165,13 +4165,13 @@
         <v>10.3</v>
       </c>
       <c r="H64" t="str">
-        <v>-</v>
+        <v>22년07월_최초발생</v>
       </c>
       <c r="I64" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J64" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" t="str">
         <v>0</v>
@@ -4183,22 +4183,22 @@
         <v>0</v>
       </c>
       <c r="N64" t="str">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O64" t="str">
-        <v>일반</v>
+        <v>긴급</v>
       </c>
       <c r="P64" t="str">
-        <v>-</v>
+        <v>10cm이상 보도침하</v>
       </c>
       <c r="Q64" t="str">
-        <v>이의동1322</v>
+        <v>이의동421-5</v>
       </c>
       <c r="R64" t="str">
         <v/>
       </c>
       <c r="S64" t="str">
-        <v>광교 비지니스센터 앞 도로(광교로152))</v>
+        <v>입출고선환기구 옆 보도</v>
       </c>
       <c r="T64" t="str">
         <v/>
@@ -4206,19 +4206,19 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>26-23</v>
+        <v>26-24</v>
       </c>
       <c r="B65" t="str">
         <v>광교로</v>
       </c>
       <c r="C65" t="str">
-        <v>26-수원시-23</v>
+        <v>26-수원시-24</v>
       </c>
       <c r="D65" t="str">
-        <v>불량</v>
+        <v>양호</v>
       </c>
       <c r="E65" t="str">
-        <v>양호</v>
+        <v>거북등</v>
       </c>
       <c r="F65" t="str">
         <v>양호</v>
@@ -4227,13 +4227,13 @@
         <v>10.3</v>
       </c>
       <c r="H65" t="str">
-        <v>22년07월_최초발생</v>
+        <v>-</v>
       </c>
       <c r="I65" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J65" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K65" t="str">
         <v>0</v>
@@ -4245,13 +4245,13 @@
         <v>0</v>
       </c>
       <c r="N65" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O65" t="str">
-        <v>긴급</v>
+        <v>일반</v>
       </c>
       <c r="P65" t="str">
-        <v>10cm이상 보도침하</v>
+        <v>-</v>
       </c>
       <c r="Q65" t="str">
         <v>이의동421-5</v>
@@ -4260,7 +4260,7 @@
         <v/>
       </c>
       <c r="S65" t="str">
-        <v>입출고선환기구 옆 보도</v>
+        <v>입출고선환기구 옆 도로</v>
       </c>
       <c r="T65" t="str">
         <v/>
@@ -4268,13 +4268,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>26-24</v>
+        <v>26-25</v>
       </c>
       <c r="B66" t="str">
         <v>광교로</v>
       </c>
       <c r="C66" t="str">
-        <v>26-수원시-24</v>
+        <v>26-수원시-25</v>
       </c>
       <c r="D66" t="str">
         <v>양호</v>
@@ -4316,13 +4316,13 @@
         <v>-</v>
       </c>
       <c r="Q66" t="str">
-        <v>이의동421-5</v>
+        <v>이의동1322-2</v>
       </c>
       <c r="R66" t="str">
         <v/>
       </c>
       <c r="S66" t="str">
-        <v>입출고선환기구 옆 도로</v>
+        <v>광교사거리 전 도로</v>
       </c>
       <c r="T66" t="str">
         <v/>
@@ -4330,19 +4330,19 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>26-25</v>
+        <v>26-14</v>
       </c>
       <c r="B67" t="str">
-        <v>광교로</v>
+        <v>도청로</v>
       </c>
       <c r="C67" t="str">
-        <v>26-수원시-25</v>
+        <v>26-수원시-14</v>
       </c>
       <c r="D67" t="str">
         <v>양호</v>
       </c>
       <c r="E67" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F67" t="str">
         <v>양호</v>
@@ -4357,7 +4357,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K67" t="str">
         <v>0</v>
@@ -4369,22 +4369,22 @@
         <v>0</v>
       </c>
       <c r="N67" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O67" t="str">
         <v>일반</v>
       </c>
       <c r="P67" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q67" t="str">
-        <v>이의동1322-2</v>
+        <v>이의동1344</v>
       </c>
       <c r="R67" t="str">
         <v/>
       </c>
       <c r="S67" t="str">
-        <v>광교사거리 전 도로</v>
+        <v>자연앤 힐스테이트 자이언트리딩 / 하선시점 피난계단 뒤 도로(도청로65)</v>
       </c>
       <c r="T67" t="str">
         <v/>
@@ -4392,19 +4392,19 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>26-14</v>
+        <v>26-15</v>
       </c>
       <c r="B68" t="str">
         <v>도청로</v>
       </c>
       <c r="C68" t="str">
-        <v>26-수원시-14</v>
+        <v>26-수원시-15</v>
       </c>
       <c r="D68" t="str">
-        <v>양호</v>
+        <v>불량</v>
       </c>
       <c r="E68" t="str">
-        <v>횡균열</v>
+        <v>양호</v>
       </c>
       <c r="F68" t="str">
         <v>양호</v>
@@ -4413,13 +4413,13 @@
         <v>10.3</v>
       </c>
       <c r="H68" t="str">
-        <v>-</v>
+        <v>24년_확인</v>
       </c>
       <c r="I68" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J68" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="str">
         <v>0</v>
@@ -4431,13 +4431,13 @@
         <v>0</v>
       </c>
       <c r="N68" t="str">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O68" t="str">
-        <v>일반</v>
+        <v>긴급</v>
       </c>
       <c r="P68" t="str">
-        <v>5cm이하 침하</v>
+        <v>11cm이상 보도침하</v>
       </c>
       <c r="Q68" t="str">
         <v>이의동1344</v>
@@ -4446,77 +4446,15 @@
         <v/>
       </c>
       <c r="S68" t="str">
-        <v>자연앤 힐스테이트 자이언트리딩 / 하선시점 피난계단 뒤 도로(도청로65)</v>
+        <v>자연앤 힐스테이트 자이언트리딩 / 하선시점 피난계단 뒤 보도(도청로65)</v>
       </c>
       <c r="T68" t="str">
         <v>현장확인필요</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>26-15</v>
-      </c>
-      <c r="B69" t="str">
-        <v>도청로</v>
-      </c>
-      <c r="C69" t="str">
-        <v>26-수원시-15</v>
-      </c>
-      <c r="D69" t="str">
-        <v>불량</v>
-      </c>
-      <c r="E69" t="str">
-        <v>양호</v>
-      </c>
-      <c r="F69" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G69" t="str">
-        <v>10.3</v>
-      </c>
-      <c r="H69" t="str">
-        <v>-</v>
-      </c>
-      <c r="I69" t="str">
-        <v>9</v>
-      </c>
-      <c r="J69" t="str">
-        <v>0</v>
-      </c>
-      <c r="K69" t="str">
-        <v>0</v>
-      </c>
-      <c r="L69" t="str">
-        <v>1</v>
-      </c>
-      <c r="M69" t="str">
-        <v>0</v>
-      </c>
-      <c r="N69" t="str">
-        <v>10</v>
-      </c>
-      <c r="O69" t="str">
-        <v>긴급</v>
-      </c>
-      <c r="P69" t="str">
-        <v>11cm이상 보도침하</v>
-      </c>
-      <c r="Q69" t="str">
-        <v>이의동1344</v>
-      </c>
-      <c r="R69" t="str">
-        <v/>
-      </c>
-      <c r="S69" t="str">
-        <v>자연앤 힐스테이트 자이언트리딩 / 하선시점 피난계단 뒤 보도(도청로65)</v>
-      </c>
-      <c r="T69" t="str">
-        <v>현장확인필요</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T68"/>
   </ignoredErrors>
 </worksheet>
 </file>